--- a/Dowling/dowling-vs-johnston-090426.xlsx
+++ b/Dowling/dowling-vs-johnston-090426.xlsx
@@ -5,7 +5,7 @@
     <workbookView/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="R0ec4b2819e5d4147"/>
+    <sheet name="Sheet1" sheetId="1" r:id="R17ff3dbfff8e4dbf"/>
   </sheets>
 </workbook>
 </file>
@@ -196,6 +196,12 @@
     <t>D</t>
   </si>
   <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
     <t>Penalty</t>
   </si>
   <si>
@@ -226,6 +232,9 @@
     <t>KO</t>
   </si>
   <si>
+    <t>C</t>
+  </si>
+  <si>
     <t>Y OFF PRO</t>
   </si>
   <si>
@@ -281,6 +290,9 @@
   </si>
   <si>
     <t>Complete, Fumble</t>
+  </si>
+  <si>
+    <t>E-Alley</t>
   </si>
   <si>
     <t>WING TRIPS</t>
@@ -536,6 +548,9 @@
       <c r="N4">
         <v>25</v>
       </c>
+      <c r="O4">
+        <v>9</v>
+      </c>
       <c r="R4" t="s">
         <v>34</v>
       </c>
@@ -836,6 +851,9 @@
       <c r="N10">
         <v>9</v>
       </c>
+      <c r="O10">
+        <v>3</v>
+      </c>
       <c r="R10" t="s">
         <v>30</v>
       </c>
@@ -894,6 +912,9 @@
       </c>
       <c r="N11">
         <v>15</v>
+      </c>
+      <c r="O11">
+        <v>6</v>
       </c>
       <c r="R11" t="s">
         <v>30</v>
@@ -1160,6 +1181,9 @@
       <c r="L16">
         <v>6</v>
       </c>
+      <c r="M16" t="s">
+        <v>61</v>
+      </c>
       <c r="R16" t="s">
         <v>34</v>
       </c>
@@ -1213,6 +1237,9 @@
       <c r="L17">
         <v>7</v>
       </c>
+      <c r="M17" t="s">
+        <v>62</v>
+      </c>
       <c r="R17" t="s">
         <v>34</v>
       </c>
@@ -1252,7 +1279,7 @@
         <v>30</v>
       </c>
       <c r="I18" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J18">
         <v>5</v>
@@ -1310,6 +1337,9 @@
       <c r="N19">
         <v>14</v>
       </c>
+      <c r="O19">
+        <v>4</v>
+      </c>
       <c r="R19" t="s">
         <v>34</v>
       </c>
@@ -1352,10 +1382,10 @@
         <v>30</v>
       </c>
       <c r="H20" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I20" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="Q20">
         <v>15</v>
@@ -1408,7 +1438,7 @@
         <v>39</v>
       </c>
       <c r="T21" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="U21" t="s">
         <v>30</v>
@@ -1455,7 +1485,7 @@
         <v>7</v>
       </c>
       <c r="T22" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="U22" t="s">
         <v>34</v>
@@ -1543,7 +1573,7 @@
         <v>31</v>
       </c>
       <c r="I24" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="J24">
         <v>10</v>
@@ -1561,7 +1591,7 @@
         <v>54</v>
       </c>
       <c r="T24" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="U24" t="s">
         <v>30</v>
@@ -1596,10 +1626,10 @@
         <v>26</v>
       </c>
       <c r="H25" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I25" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="X25">
         <v>2</v>
@@ -1628,7 +1658,7 @@
         <v>26</v>
       </c>
       <c r="H26" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I26" t="s">
         <v>28</v>
@@ -1674,6 +1704,9 @@
       <c r="L27">
         <v>6</v>
       </c>
+      <c r="M27" t="s">
+        <v>73</v>
+      </c>
       <c r="R27" t="s">
         <v>34</v>
       </c>
@@ -1730,11 +1763,14 @@
       <c r="N28">
         <v>42</v>
       </c>
+      <c r="O28">
+        <v>9</v>
+      </c>
       <c r="R28" t="s">
         <v>34</v>
       </c>
       <c r="S28" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="U28" t="s">
         <v>34</v>
@@ -1793,7 +1829,7 @@
         <v>34</v>
       </c>
       <c r="W29" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="X29">
         <v>3</v>
@@ -1839,6 +1875,9 @@
       <c r="N30">
         <v>11</v>
       </c>
+      <c r="O30">
+        <v>5</v>
+      </c>
       <c r="R30" t="s">
         <v>30</v>
       </c>
@@ -1891,6 +1930,9 @@
       </c>
       <c r="L31">
         <v>6</v>
+      </c>
+      <c r="M31" t="s">
+        <v>61</v>
       </c>
       <c r="R31" t="s">
         <v>30</v>
@@ -1937,7 +1979,7 @@
         <v>37</v>
       </c>
       <c r="I32" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="J32">
         <v>56</v>
@@ -1951,11 +1993,14 @@
       <c r="N32">
         <v>12</v>
       </c>
+      <c r="O32">
+        <v>5</v>
+      </c>
       <c r="R32" t="s">
         <v>30</v>
       </c>
       <c r="S32" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="U32" t="s">
         <v>30</v>
@@ -1993,10 +2038,10 @@
         <v>26</v>
       </c>
       <c r="H33" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I33" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="X33">
         <v>3</v>
@@ -2060,7 +2105,7 @@
         <v>37</v>
       </c>
       <c r="I35" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="J35">
         <v>80</v>
@@ -2074,6 +2119,9 @@
       <c r="N35">
         <v>9</v>
       </c>
+      <c r="O35">
+        <v>2</v>
+      </c>
       <c r="R35" t="s">
         <v>49</v>
       </c>
@@ -2081,7 +2129,7 @@
         <v>50</v>
       </c>
       <c r="T35" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="U35" t="s">
         <v>34</v>
@@ -2113,10 +2161,10 @@
         <v>26</v>
       </c>
       <c r="H36" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I36" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="X36">
         <v>3</v>
@@ -2145,10 +2193,10 @@
         <v>26</v>
       </c>
       <c r="H37" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I37" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="Q37">
         <v>20</v>
@@ -2194,6 +2242,9 @@
       <c r="L38">
         <v>7</v>
       </c>
+      <c r="M38" t="s">
+        <v>61</v>
+      </c>
       <c r="R38" t="s">
         <v>30</v>
       </c>
@@ -2250,6 +2301,9 @@
       <c r="N39">
         <v>7</v>
       </c>
+      <c r="O39">
+        <v>2</v>
+      </c>
       <c r="R39" t="s">
         <v>34</v>
       </c>
@@ -2306,11 +2360,14 @@
       <c r="N40">
         <v>5</v>
       </c>
+      <c r="O40">
+        <v>3</v>
+      </c>
       <c r="R40" t="s">
         <v>49</v>
       </c>
       <c r="S40" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="U40" t="s">
         <v>34</v>
@@ -2348,7 +2405,7 @@
         <v>37</v>
       </c>
       <c r="I41" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="J41">
         <v>0</v>
@@ -2361,6 +2418,9 @@
       </c>
       <c r="N41">
         <v>21</v>
+      </c>
+      <c r="O41">
+        <v>5</v>
       </c>
       <c r="R41" t="s">
         <v>30</v>
@@ -2407,7 +2467,7 @@
         <v>31</v>
       </c>
       <c r="I42" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="J42">
         <v>61</v>
@@ -2422,10 +2482,10 @@
         <v>34</v>
       </c>
       <c r="S42" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="T42" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="U42" t="s">
         <v>34</v>
@@ -2457,10 +2517,10 @@
         <v>26</v>
       </c>
       <c r="H43" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I43" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="X43">
         <v>4</v>
@@ -2489,7 +2549,7 @@
         <v>26</v>
       </c>
       <c r="H44" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I44" t="s">
         <v>28</v>
@@ -2535,6 +2595,9 @@
       <c r="L45">
         <v>6</v>
       </c>
+      <c r="M45" t="s">
+        <v>73</v>
+      </c>
       <c r="R45" t="s">
         <v>34</v>
       </c>
@@ -2591,11 +2654,14 @@
       <c r="N46">
         <v>0</v>
       </c>
+      <c r="O46">
+        <v>2</v>
+      </c>
       <c r="R46" t="s">
         <v>34</v>
       </c>
       <c r="S46" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="U46" t="s">
         <v>34</v>
@@ -2647,11 +2713,14 @@
       <c r="N47">
         <v>0</v>
       </c>
+      <c r="O47">
+        <v>2</v>
+      </c>
       <c r="R47" t="s">
         <v>30</v>
       </c>
       <c r="S47" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="U47" t="s">
         <v>30</v>
@@ -2689,7 +2758,7 @@
         <v>31</v>
       </c>
       <c r="I48" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J48">
         <v>-5</v>
@@ -2742,7 +2811,7 @@
         <v>37</v>
       </c>
       <c r="I49" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="J49">
         <v>-3</v>
@@ -2806,11 +2875,14 @@
       <c r="L50">
         <v>6</v>
       </c>
+      <c r="M50" t="s">
+        <v>61</v>
+      </c>
       <c r="R50" t="s">
         <v>49</v>
       </c>
       <c r="S50" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="U50" t="s">
         <v>34</v>
@@ -2851,7 +2923,7 @@
         <v>37</v>
       </c>
       <c r="I51" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="J51">
         <v>76</v>
@@ -2865,11 +2937,14 @@
       <c r="N51">
         <v>44</v>
       </c>
+      <c r="O51">
+        <v>7</v>
+      </c>
       <c r="R51" t="s">
         <v>49</v>
       </c>
       <c r="S51" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="U51" t="s">
         <v>30</v>
@@ -2904,10 +2979,10 @@
         <v>26</v>
       </c>
       <c r="H52" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I52" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="X52">
         <v>5</v>
@@ -2989,7 +3064,7 @@
         <v>39</v>
       </c>
       <c r="T54" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="U54" t="s">
         <v>34</v>
@@ -3045,7 +3120,7 @@
         <v>50</v>
       </c>
       <c r="T55" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="U55" t="s">
         <v>30</v>
@@ -3095,10 +3170,10 @@
         <v>34</v>
       </c>
       <c r="S56" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="T56" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="U56" t="s">
         <v>30</v>
@@ -3147,6 +3222,9 @@
       <c r="N57">
         <v>19</v>
       </c>
+      <c r="O57">
+        <v>6</v>
+      </c>
       <c r="R57" t="s">
         <v>34</v>
       </c>
@@ -3207,7 +3285,7 @@
         <v>35</v>
       </c>
       <c r="T58" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="U58" t="s">
         <v>34</v>
@@ -3245,7 +3323,7 @@
         <v>43</v>
       </c>
       <c r="I59" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="X59">
         <v>5</v>
@@ -3277,7 +3355,7 @@
         <v>31</v>
       </c>
       <c r="I60" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="J60">
         <v>84</v>
@@ -3287,6 +3365,9 @@
       </c>
       <c r="L60">
         <v>6</v>
+      </c>
+      <c r="M60" t="s">
+        <v>73</v>
       </c>
       <c r="Q60">
         <v>0</v>
@@ -3333,10 +3414,10 @@
         <v>26</v>
       </c>
       <c r="H61" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I61" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="X61">
         <v>6</v>
@@ -3415,10 +3496,10 @@
         <v>30</v>
       </c>
       <c r="S63" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="T63" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="U63" t="s">
         <v>34</v>
@@ -3474,7 +3555,7 @@
         <v>35</v>
       </c>
       <c r="T64" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="U64" t="s">
         <v>30</v>
@@ -3580,10 +3661,10 @@
         <v>30</v>
       </c>
       <c r="S66" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="T66" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="U66" t="s">
         <v>34</v>
@@ -3674,7 +3755,7 @@
         <v>37</v>
       </c>
       <c r="I68" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="J68">
         <v>57</v>
@@ -3687,6 +3768,9 @@
       </c>
       <c r="N68">
         <v>19</v>
+      </c>
+      <c r="O68">
+        <v>5</v>
       </c>
       <c r="R68" t="s">
         <v>34</v>
@@ -3741,11 +3825,14 @@
       <c r="L69">
         <v>8</v>
       </c>
+      <c r="M69" t="s">
+        <v>61</v>
+      </c>
       <c r="R69" t="s">
         <v>34</v>
       </c>
       <c r="S69" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="U69" t="s">
         <v>34</v>
@@ -3794,11 +3881,14 @@
       <c r="L70">
         <v>7</v>
       </c>
+      <c r="M70" t="s">
+        <v>93</v>
+      </c>
       <c r="R70" t="s">
         <v>34</v>
       </c>
       <c r="S70" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="U70" t="s">
         <v>34</v>
@@ -3853,11 +3943,14 @@
       <c r="N71">
         <v>41</v>
       </c>
+      <c r="O71">
+        <v>8</v>
+      </c>
       <c r="R71" t="s">
         <v>30</v>
       </c>
       <c r="S71" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="U71" t="s">
         <v>30</v>
@@ -3892,10 +3985,10 @@
         <v>34</v>
       </c>
       <c r="H72" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I72" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="X72">
         <v>7</v>
@@ -3941,14 +4034,17 @@
       <c r="N73">
         <v>5</v>
       </c>
+      <c r="O73">
+        <v>3</v>
+      </c>
       <c r="R73" t="s">
         <v>34</v>
       </c>
       <c r="S73" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="T73" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="U73" t="s">
         <v>34</v>
@@ -4057,7 +4153,7 @@
         <v>39</v>
       </c>
       <c r="T75" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="U75" t="s">
         <v>30</v>
@@ -4110,7 +4206,7 @@
         <v>35</v>
       </c>
       <c r="T76" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="U76" t="s">
         <v>34</v>
@@ -4145,10 +4241,10 @@
         <v>34</v>
       </c>
       <c r="H77" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="I77" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="X77">
         <v>7</v>
@@ -4177,7 +4273,7 @@
         <v>26</v>
       </c>
       <c r="H78" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I78" t="s">
         <v>28</v>
@@ -4226,6 +4322,9 @@
       <c r="N79">
         <v>10</v>
       </c>
+      <c r="O79">
+        <v>4</v>
+      </c>
       <c r="R79" t="s">
         <v>34</v>
       </c>
@@ -4279,11 +4378,14 @@
       <c r="L80">
         <v>7</v>
       </c>
+      <c r="M80" t="s">
+        <v>62</v>
+      </c>
       <c r="R80" t="s">
         <v>49</v>
       </c>
       <c r="S80" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="U80" t="s">
         <v>34</v>
@@ -4321,7 +4423,7 @@
         <v>26</v>
       </c>
       <c r="I81" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="J81">
         <v>0</v>
@@ -4373,11 +4475,14 @@
       <c r="N82">
         <v>32</v>
       </c>
+      <c r="O82">
+        <v>9</v>
+      </c>
       <c r="R82" t="s">
         <v>49</v>
       </c>
       <c r="S82" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="U82" t="s">
         <v>34</v>
@@ -4482,11 +4587,14 @@
       <c r="N84">
         <v>8</v>
       </c>
+      <c r="O84">
+        <v>3</v>
+      </c>
       <c r="R84" t="s">
         <v>34</v>
       </c>
       <c r="S84" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U84" t="s">
         <v>34</v>
@@ -4521,7 +4629,7 @@
         <v>37</v>
       </c>
       <c r="I85" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="J85">
         <v>10</v>
@@ -4535,11 +4643,14 @@
       <c r="N85">
         <v>15</v>
       </c>
+      <c r="O85">
+        <v>4</v>
+      </c>
       <c r="R85" t="s">
         <v>34</v>
       </c>
       <c r="S85" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="U85" t="s">
         <v>30</v>
@@ -4574,10 +4685,10 @@
         <v>26</v>
       </c>
       <c r="H86" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I86" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="X86">
         <v>7</v>
@@ -4656,10 +4767,10 @@
         <v>30</v>
       </c>
       <c r="S88" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="T88" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="U88" t="s">
         <v>34</v>
@@ -4715,7 +4826,7 @@
         <v>39</v>
       </c>
       <c r="T89" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="U89" t="s">
         <v>34</v>
@@ -4768,7 +4879,7 @@
         <v>50</v>
       </c>
       <c r="T90" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="U90" t="s">
         <v>34</v>
@@ -4818,10 +4929,10 @@
         <v>30</v>
       </c>
       <c r="S91" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="T91" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="U91" t="s">
         <v>30</v>
@@ -4856,7 +4967,7 @@
         <v>37</v>
       </c>
       <c r="I92" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="J92">
         <v>65</v>
@@ -4870,6 +4981,9 @@
       <c r="N92">
         <v>38</v>
       </c>
+      <c r="O92">
+        <v>8</v>
+      </c>
       <c r="R92" t="s">
         <v>34</v>
       </c>
@@ -4877,7 +4991,7 @@
         <v>35</v>
       </c>
       <c r="T92" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="U92" t="s">
         <v>34</v>
@@ -4909,10 +5023,10 @@
         <v>30</v>
       </c>
       <c r="H93" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="I93" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="U93" t="s">
         <v>34</v>
@@ -4947,7 +5061,7 @@
         <v>26</v>
       </c>
       <c r="H94" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I94" t="s">
         <v>28</v>
@@ -4993,6 +5107,9 @@
       <c r="L95">
         <v>6</v>
       </c>
+      <c r="M95" t="s">
+        <v>73</v>
+      </c>
       <c r="R95" t="s">
         <v>30</v>
       </c>
@@ -5052,6 +5169,9 @@
       <c r="N96">
         <v>7</v>
       </c>
+      <c r="O96">
+        <v>3</v>
+      </c>
       <c r="R96" t="s">
         <v>30</v>
       </c>
@@ -5111,6 +5231,9 @@
       <c r="N97">
         <v>13</v>
       </c>
+      <c r="O97">
+        <v>6</v>
+      </c>
       <c r="R97" t="s">
         <v>30</v>
       </c>
@@ -5167,11 +5290,14 @@
       <c r="N98">
         <v>9</v>
       </c>
+      <c r="O98">
+        <v>3</v>
+      </c>
       <c r="R98" t="s">
         <v>34</v>
       </c>
       <c r="S98" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="U98" t="s">
         <v>34</v>
@@ -5223,6 +5349,9 @@
       <c r="N99">
         <v>10</v>
       </c>
+      <c r="O99">
+        <v>5</v>
+      </c>
       <c r="R99" t="s">
         <v>30</v>
       </c>
@@ -5273,6 +5402,9 @@
       <c r="L100">
         <v>6</v>
       </c>
+      <c r="M100" t="s">
+        <v>93</v>
+      </c>
       <c r="R100" t="s">
         <v>34</v>
       </c>
@@ -5315,7 +5447,7 @@
         <v>30</v>
       </c>
       <c r="I101" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J101">
         <v>5</v>
@@ -5376,11 +5508,14 @@
       <c r="N102">
         <v>10</v>
       </c>
+      <c r="O102">
+        <v>4</v>
+      </c>
       <c r="R102" t="s">
         <v>34</v>
       </c>
       <c r="S102" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U102" t="s">
         <v>30</v>
@@ -5426,6 +5561,9 @@
       <c r="L103">
         <v>6</v>
       </c>
+      <c r="M103" t="s">
+        <v>62</v>
+      </c>
       <c r="R103" t="s">
         <v>34</v>
       </c>
@@ -5439,7 +5577,7 @@
         <v>30</v>
       </c>
       <c r="W103" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="X103">
         <v>8</v>
@@ -5471,7 +5609,7 @@
         <v>37</v>
       </c>
       <c r="I104" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="J104">
         <v>-4</v>
@@ -5486,7 +5624,7 @@
         <v>49</v>
       </c>
       <c r="S104" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="U104" t="s">
         <v>30</v>
@@ -5521,10 +5659,10 @@
         <v>30</v>
       </c>
       <c r="H105" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I105" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="X105">
         <v>8</v>
@@ -5574,7 +5712,7 @@
         <v>30</v>
       </c>
       <c r="S106" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U106" t="s">
         <v>30</v>
@@ -5673,6 +5811,9 @@
       <c r="N108">
         <v>13</v>
       </c>
+      <c r="O108">
+        <v>6</v>
+      </c>
       <c r="R108" t="s">
         <v>30</v>
       </c>
@@ -5862,7 +6003,7 @@
         <v>34</v>
       </c>
       <c r="I112" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="J112">
         <v>0</v>
@@ -6000,7 +6141,7 @@
         <v>37</v>
       </c>
       <c r="I115" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="J115">
         <v>-9</v>
@@ -6093,6 +6234,9 @@
       <c r="L117">
         <v>6</v>
       </c>
+      <c r="M117" t="s">
+        <v>61</v>
+      </c>
       <c r="R117" t="s">
         <v>34</v>
       </c>
@@ -6152,6 +6296,9 @@
       <c r="N118">
         <v>11</v>
       </c>
+      <c r="O118">
+        <v>5</v>
+      </c>
       <c r="R118" t="s">
         <v>34</v>
       </c>
@@ -6162,7 +6309,7 @@
         <v>34</v>
       </c>
       <c r="W118" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="X118">
         <v>9</v>
@@ -6194,7 +6341,7 @@
         <v>37</v>
       </c>
       <c r="I119" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="J119">
         <v>-11</v>
@@ -6247,10 +6394,10 @@
         <v>34</v>
       </c>
       <c r="H120" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I120" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="Q120">
         <v>11</v>
@@ -6349,11 +6496,14 @@
       <c r="N122">
         <v>6</v>
       </c>
+      <c r="O122">
+        <v>1</v>
+      </c>
       <c r="R122" t="s">
         <v>30</v>
       </c>
       <c r="S122" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U122" t="s">
         <v>30</v>
@@ -6388,7 +6538,7 @@
         <v>37</v>
       </c>
       <c r="I123" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="J123">
         <v>40</v>
@@ -6402,11 +6552,14 @@
       <c r="N123">
         <v>40</v>
       </c>
+      <c r="O123">
+        <v>9</v>
+      </c>
       <c r="R123" t="s">
         <v>49</v>
       </c>
       <c r="S123" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="U123" t="s">
         <v>34</v>
@@ -6441,10 +6594,10 @@
         <v>26</v>
       </c>
       <c r="H124" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I124" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="X124">
         <v>11</v>
@@ -6473,10 +6626,10 @@
         <v>26</v>
       </c>
       <c r="H125" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I125" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="Q125">
         <v>17</v>
@@ -6522,6 +6675,9 @@
       <c r="L126">
         <v>5</v>
       </c>
+      <c r="M126" t="s">
+        <v>61</v>
+      </c>
       <c r="R126" t="s">
         <v>34</v>
       </c>
@@ -6575,6 +6731,12 @@
       <c r="L127">
         <v>5</v>
       </c>
+      <c r="N127">
+        <v>12</v>
+      </c>
+      <c r="O127">
+        <v>5</v>
+      </c>
       <c r="R127" t="s">
         <v>34</v>
       </c>
@@ -6628,6 +6790,9 @@
       <c r="N128">
         <v>17</v>
       </c>
+      <c r="O128">
+        <v>4</v>
+      </c>
       <c r="R128" t="s">
         <v>34</v>
       </c>
@@ -6667,10 +6832,10 @@
         <v>30</v>
       </c>
       <c r="H129" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="I129" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="X129">
         <v>10</v>
@@ -6717,7 +6882,7 @@
         <v>34</v>
       </c>
       <c r="S130" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="U130" t="s">
         <v>34</v>
@@ -6755,7 +6920,7 @@
         <v>31</v>
       </c>
       <c r="I131" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J131">
         <v>-5</v>
@@ -6817,7 +6982,7 @@
         <v>30</v>
       </c>
       <c r="S132" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="U132" t="s">
         <v>34</v>
@@ -6867,7 +7032,7 @@
         <v>34</v>
       </c>
       <c r="S133" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="U133" t="s">
         <v>34</v>
@@ -6920,7 +7085,7 @@
         <v>30</v>
       </c>
       <c r="S134" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="U134" t="s">
         <v>30</v>
@@ -6952,10 +7117,10 @@
         <v>30</v>
       </c>
       <c r="H135" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="I135" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="X135">
         <v>12</v>
@@ -6984,7 +7149,7 @@
         <v>26</v>
       </c>
       <c r="H136" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I136" t="s">
         <v>28</v>
@@ -7019,7 +7184,7 @@
         <v>37</v>
       </c>
       <c r="I137" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="J137">
         <v>80</v>
@@ -7032,6 +7197,9 @@
       </c>
       <c r="N137">
         <v>0</v>
+      </c>
+      <c r="O137">
+        <v>1</v>
       </c>
       <c r="R137" t="s">
         <v>34</v>
@@ -7072,10 +7240,10 @@
         <v>26</v>
       </c>
       <c r="H138" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="I138" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="X138">
         <v>11</v>
@@ -7154,7 +7322,7 @@
         <v>34</v>
       </c>
       <c r="S140" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="U140" t="s">
         <v>34</v>
@@ -7257,7 +7425,7 @@
         <v>34</v>
       </c>
       <c r="S142" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="U142" t="s">
         <v>30</v>
@@ -7360,7 +7528,7 @@
         <v>30</v>
       </c>
       <c r="S144" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="U144" t="s">
         <v>30</v>
@@ -7392,10 +7560,10 @@
         <v>30</v>
       </c>
       <c r="H145" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="I145" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="X145">
         <v>13</v>
@@ -7424,7 +7592,7 @@
         <v>26</v>
       </c>
       <c r="H146" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I146" t="s">
         <v>28</v>
@@ -7473,11 +7641,14 @@
       <c r="N147">
         <v>18</v>
       </c>
+      <c r="O147">
+        <v>4</v>
+      </c>
       <c r="R147" t="s">
         <v>49</v>
       </c>
       <c r="S147" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="U147" t="s">
         <v>30</v>
@@ -7529,6 +7700,9 @@
       <c r="N148">
         <v>13</v>
       </c>
+      <c r="O148">
+        <v>4</v>
+      </c>
       <c r="R148" t="s">
         <v>34</v>
       </c>
@@ -7638,6 +7812,9 @@
       <c r="N150">
         <v>20</v>
       </c>
+      <c r="O150">
+        <v>9</v>
+      </c>
       <c r="R150" t="s">
         <v>30</v>
       </c>
@@ -7694,6 +7871,9 @@
       <c r="N151">
         <v>15</v>
       </c>
+      <c r="O151">
+        <v>4</v>
+      </c>
       <c r="R151" t="s">
         <v>30</v>
       </c>
@@ -7750,6 +7930,9 @@
       <c r="N152">
         <v>11</v>
       </c>
+      <c r="O152">
+        <v>4</v>
+      </c>
       <c r="R152" t="s">
         <v>30</v>
       </c>
@@ -7804,7 +7987,7 @@
         <v>49</v>
       </c>
       <c r="S153" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="X153">
         <v>14</v>

--- a/Dowling/dowling-vs-johnston-090426.xlsx
+++ b/Dowling/dowling-vs-johnston-090426.xlsx
@@ -5,7 +5,7 @@
     <workbookView/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="R17ff3dbfff8e4dbf"/>
+    <sheet name="Sheet1" sheetId="1" r:id="R9faea165ebb64be7"/>
   </sheets>
 </workbook>
 </file>
@@ -58,6 +58,21 @@
     <t>PASS ZONE</t>
   </si>
   <si>
+    <t>BACKFIELD</t>
+  </si>
+  <si>
+    <t>DEF FRONT</t>
+  </si>
+  <si>
+    <t>FRONT MOVEMENT</t>
+  </si>
+  <si>
+    <t>COVERAGE</t>
+  </si>
+  <si>
+    <t>BLITZ</t>
+  </si>
+  <si>
     <t>KICK YARDS</t>
   </si>
   <si>
@@ -79,9 +94,6 @@
     <t>MOTION DIR</t>
   </si>
   <si>
-    <t>COVERAGE</t>
-  </si>
-  <si>
     <t>SERIES</t>
   </si>
   <si>
@@ -115,6 +127,9 @@
     <t>N</t>
   </si>
   <si>
+    <t>G</t>
+  </si>
+  <si>
     <t>R</t>
   </si>
   <si>
@@ -139,6 +154,9 @@
     <t>Scramble</t>
   </si>
   <si>
+    <t>DOT</t>
+  </si>
+  <si>
     <t>BOUND PIPE COVER SWITCH</t>
   </si>
   <si>
@@ -151,6 +169,9 @@
     <t>Y</t>
   </si>
   <si>
+    <t>G GUN</t>
+  </si>
+  <si>
     <t>MIRROR BULLDOGS CLEAR JOHN</t>
   </si>
   <si>
@@ -187,6 +208,9 @@
     <t>MIRROR BULLDOGS EGYPT</t>
   </si>
   <si>
+    <t>DOT UNDER</t>
+  </si>
+  <si>
     <t>Y TRIPS CLOSED</t>
   </si>
   <si>
@@ -199,9 +223,18 @@
     <t>B</t>
   </si>
   <si>
+    <t>K GUN</t>
+  </si>
+  <si>
+    <t>MIAMI</t>
+  </si>
+  <si>
     <t>A</t>
   </si>
   <si>
+    <t>STR TEX</t>
+  </si>
+  <si>
     <t>Penalty</t>
   </si>
   <si>
@@ -214,6 +247,9 @@
     <t>BREAK Q HAWKEYES KEY 3</t>
   </si>
   <si>
+    <t>Q</t>
+  </si>
+  <si>
     <t>BREAK Q HAWKEYES H PIPE</t>
   </si>
   <si>
@@ -235,9 +271,15 @@
     <t>C</t>
   </si>
   <si>
+    <t>TANGO</t>
+  </si>
+  <si>
     <t>Y OFF PRO</t>
   </si>
   <si>
+    <t>DUKE</t>
+  </si>
+  <si>
     <t>IOWA ROBBER</t>
   </si>
   <si>
@@ -253,6 +295,12 @@
     <t>HAWKEYES C</t>
   </si>
   <si>
+    <t>STR EXIT</t>
+  </si>
+  <si>
+    <t>WK EXIT</t>
+  </si>
+  <si>
     <t>ACE</t>
   </si>
   <si>
@@ -265,12 +313,21 @@
     <t>MIRROR PANTHERS</t>
   </si>
   <si>
+    <t>K TUCK G</t>
+  </si>
+  <si>
     <t>TWINS OVER</t>
   </si>
   <si>
     <t>Sack</t>
   </si>
   <si>
+    <t>FLEX</t>
+  </si>
+  <si>
+    <t>FLEX TANGO</t>
+  </si>
+  <si>
     <t>ARROW ICE Q MIRROR BULLDOGS</t>
   </si>
   <si>
@@ -286,6 +343,9 @@
     <t>PATRIOTS CLEAR JOHN</t>
   </si>
   <si>
+    <t>K TUCK DOT</t>
+  </si>
+  <si>
     <t>PRO</t>
   </si>
   <si>
@@ -316,6 +376,18 @@
     <t>Timeout</t>
   </si>
   <si>
+    <t>OLE MISS</t>
+  </si>
+  <si>
+    <t>WRAP</t>
+  </si>
+  <si>
+    <t>OMAHA</t>
+  </si>
+  <si>
+    <t>DBL BULLET</t>
+  </si>
+  <si>
     <t>EMPTY</t>
   </si>
   <si>
@@ -331,13 +403,31 @@
     <t>2 Pt.</t>
   </si>
   <si>
+    <t>G TUCK</t>
+  </si>
+  <si>
+    <t>IOWA</t>
+  </si>
+  <si>
+    <t>RINGO</t>
+  </si>
+  <si>
     <t>TWINS PRO</t>
   </si>
   <si>
-    <t>IOWA</t>
-  </si>
-  <si>
-    <t>3 TRAP</t>
+    <t>LUCKY</t>
+  </si>
+  <si>
+    <t>SURF</t>
+  </si>
+  <si>
+    <t>FLEX TEX</t>
+  </si>
+  <si>
+    <t>G TUCK DOT</t>
+  </si>
+  <si>
+    <t>G K DOT</t>
   </si>
   <si>
     <t>CLOSED</t>
@@ -347,7 +437,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Y153"/>
+  <dimension ref="A1:AC153"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -425,6 +515,18 @@
       <c r="Y1" t="s">
         <v>24</v>
       </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -434,7 +536,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -446,13 +548,13 @@
         <v>-40</v>
       </c>
       <c r="G2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
@@ -463,7 +565,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -475,36 +577,39 @@
         <v>-20</v>
       </c>
       <c r="G3" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H3" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I3" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J3">
         <v>3</v>
       </c>
       <c r="K3" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L3">
         <v>5</v>
       </c>
-      <c r="R3" t="s">
-        <v>34</v>
-      </c>
-      <c r="S3" t="s">
-        <v>35</v>
-      </c>
-      <c r="T3" t="s">
-        <v>36</v>
-      </c>
-      <c r="U3" t="s">
-        <v>30</v>
-      </c>
-      <c r="X3">
+      <c r="P3" t="s">
+        <v>38</v>
+      </c>
+      <c r="W3" t="s">
+        <v>39</v>
+      </c>
+      <c r="X3" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB3">
         <v>1</v>
       </c>
     </row>
@@ -516,7 +621,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D4">
         <v>2</v>
@@ -528,19 +633,19 @@
         <v>-23</v>
       </c>
       <c r="G4" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H4" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I4" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J4">
         <v>0</v>
       </c>
       <c r="K4" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L4">
         <v>6</v>
@@ -551,19 +656,22 @@
       <c r="O4">
         <v>9</v>
       </c>
-      <c r="R4" t="s">
-        <v>34</v>
-      </c>
-      <c r="S4" t="s">
-        <v>39</v>
-      </c>
-      <c r="T4" t="s">
-        <v>40</v>
-      </c>
-      <c r="U4" t="s">
-        <v>34</v>
-      </c>
-      <c r="X4">
+      <c r="P4" t="s">
+        <v>38</v>
+      </c>
+      <c r="W4" t="s">
+        <v>39</v>
+      </c>
+      <c r="X4" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB4">
         <v>1</v>
       </c>
     </row>
@@ -575,7 +683,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D5">
         <v>3</v>
@@ -587,36 +695,39 @@
         <v>-23</v>
       </c>
       <c r="G5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H5" t="s">
+        <v>42</v>
+      </c>
+      <c r="I5" t="s">
+        <v>46</v>
+      </c>
+      <c r="J5">
+        <v>2</v>
+      </c>
+      <c r="K5" t="s">
         <v>37</v>
-      </c>
-      <c r="I5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="K5" t="s">
-        <v>33</v>
       </c>
       <c r="L5">
         <v>7</v>
       </c>
-      <c r="R5" t="s">
-        <v>34</v>
-      </c>
-      <c r="S5" t="s">
-        <v>35</v>
-      </c>
-      <c r="T5" t="s">
-        <v>42</v>
-      </c>
-      <c r="U5" t="s">
-        <v>34</v>
-      </c>
-      <c r="X5">
+      <c r="P5" t="s">
+        <v>47</v>
+      </c>
+      <c r="W5" t="s">
+        <v>39</v>
+      </c>
+      <c r="X5" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB5">
         <v>1</v>
       </c>
     </row>
@@ -628,7 +739,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D6">
         <v>4</v>
@@ -640,15 +751,15 @@
         <v>-25</v>
       </c>
       <c r="G6" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H6" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I6" t="s">
-        <v>44</v>
-      </c>
-      <c r="X6">
+        <v>50</v>
+      </c>
+      <c r="AB6">
         <v>1</v>
       </c>
     </row>
@@ -660,7 +771,7 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -672,36 +783,39 @@
         <v>50</v>
       </c>
       <c r="G7" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H7" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I7" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J7">
         <v>9</v>
       </c>
       <c r="K7" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L7">
         <v>6</v>
       </c>
-      <c r="R7" t="s">
-        <v>30</v>
-      </c>
-      <c r="S7" t="s">
-        <v>39</v>
-      </c>
-      <c r="T7" t="s">
-        <v>46</v>
-      </c>
-      <c r="U7" t="s">
-        <v>30</v>
-      </c>
-      <c r="X7">
+      <c r="P7" t="s">
+        <v>52</v>
+      </c>
+      <c r="W7" t="s">
+        <v>34</v>
+      </c>
+      <c r="X7" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>53</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB7">
         <v>1</v>
       </c>
     </row>
@@ -713,7 +827,7 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D8">
         <v>2</v>
@@ -725,36 +839,39 @@
         <v>41</v>
       </c>
       <c r="G8" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H8" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I8" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J8">
         <v>10</v>
       </c>
       <c r="K8" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L8">
         <v>6</v>
       </c>
-      <c r="R8" t="s">
-        <v>30</v>
-      </c>
-      <c r="S8" t="s">
-        <v>47</v>
-      </c>
-      <c r="T8" t="s">
-        <v>48</v>
-      </c>
-      <c r="U8" t="s">
-        <v>30</v>
-      </c>
-      <c r="X8">
+      <c r="P8" t="s">
+        <v>52</v>
+      </c>
+      <c r="W8" t="s">
+        <v>34</v>
+      </c>
+      <c r="X8" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB8">
         <v>1</v>
       </c>
     </row>
@@ -766,7 +883,7 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -778,36 +895,39 @@
         <v>31</v>
       </c>
       <c r="G9" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H9" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I9" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J9">
         <v>1</v>
       </c>
       <c r="K9" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L9">
         <v>7</v>
       </c>
-      <c r="R9" t="s">
-        <v>49</v>
-      </c>
-      <c r="S9" t="s">
-        <v>50</v>
-      </c>
-      <c r="T9" t="s">
-        <v>51</v>
-      </c>
-      <c r="U9" t="s">
-        <v>34</v>
-      </c>
-      <c r="X9">
+      <c r="P9" t="s">
+        <v>47</v>
+      </c>
+      <c r="W9" t="s">
+        <v>56</v>
+      </c>
+      <c r="X9" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB9">
         <v>1</v>
       </c>
     </row>
@@ -819,7 +939,7 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D10">
         <v>2</v>
@@ -831,19 +951,19 @@
         <v>30</v>
       </c>
       <c r="G10" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H10" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I10" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J10">
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L10">
         <v>6</v>
@@ -854,22 +974,25 @@
       <c r="O10">
         <v>3</v>
       </c>
-      <c r="R10" t="s">
-        <v>30</v>
-      </c>
-      <c r="S10" t="s">
-        <v>35</v>
-      </c>
-      <c r="T10" t="s">
-        <v>52</v>
-      </c>
-      <c r="U10" t="s">
-        <v>34</v>
-      </c>
-      <c r="V10" t="s">
-        <v>30</v>
-      </c>
-      <c r="X10">
+      <c r="P10" t="s">
+        <v>38</v>
+      </c>
+      <c r="W10" t="s">
+        <v>34</v>
+      </c>
+      <c r="X10" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB10">
         <v>1</v>
       </c>
     </row>
@@ -881,7 +1004,7 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D11">
         <v>3</v>
@@ -893,19 +1016,19 @@
         <v>30</v>
       </c>
       <c r="G11" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H11" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I11" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="J11">
         <v>15</v>
       </c>
       <c r="K11" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L11">
         <v>6</v>
@@ -916,19 +1039,22 @@
       <c r="O11">
         <v>6</v>
       </c>
-      <c r="R11" t="s">
-        <v>30</v>
-      </c>
-      <c r="S11" t="s">
-        <v>54</v>
-      </c>
-      <c r="T11" t="s">
-        <v>55</v>
-      </c>
-      <c r="U11" t="s">
-        <v>34</v>
-      </c>
-      <c r="X11">
+      <c r="P11" t="s">
+        <v>38</v>
+      </c>
+      <c r="W11" t="s">
+        <v>34</v>
+      </c>
+      <c r="X11" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB11">
         <v>1</v>
       </c>
     </row>
@@ -940,7 +1066,7 @@
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -952,36 +1078,39 @@
         <v>15</v>
       </c>
       <c r="G12" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H12" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I12" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J12">
         <v>3</v>
       </c>
       <c r="K12" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L12">
         <v>5</v>
       </c>
-      <c r="R12" t="s">
-        <v>30</v>
-      </c>
-      <c r="S12" t="s">
-        <v>47</v>
-      </c>
-      <c r="T12" t="s">
-        <v>48</v>
-      </c>
-      <c r="U12" t="s">
-        <v>34</v>
-      </c>
-      <c r="X12">
+      <c r="P12" t="s">
+        <v>52</v>
+      </c>
+      <c r="W12" t="s">
+        <v>34</v>
+      </c>
+      <c r="X12" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB12">
         <v>1</v>
       </c>
     </row>
@@ -993,7 +1122,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D13">
         <v>2</v>
@@ -1005,36 +1134,39 @@
         <v>12</v>
       </c>
       <c r="G13" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H13" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I13" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J13">
         <v>3</v>
       </c>
       <c r="K13" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L13">
         <v>7</v>
       </c>
-      <c r="R13" t="s">
-        <v>49</v>
-      </c>
-      <c r="S13" t="s">
-        <v>50</v>
-      </c>
-      <c r="T13" t="s">
-        <v>51</v>
-      </c>
-      <c r="U13" t="s">
-        <v>34</v>
-      </c>
-      <c r="X13">
+      <c r="P13" t="s">
+        <v>47</v>
+      </c>
+      <c r="W13" t="s">
+        <v>56</v>
+      </c>
+      <c r="X13" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB13">
         <v>1</v>
       </c>
     </row>
@@ -1046,7 +1178,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D14">
         <v>3</v>
@@ -1058,36 +1190,39 @@
         <v>9</v>
       </c>
       <c r="G14" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H14" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I14" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J14">
         <v>3</v>
       </c>
       <c r="K14" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L14">
         <v>7</v>
       </c>
-      <c r="R14" t="s">
-        <v>30</v>
-      </c>
-      <c r="S14" t="s">
-        <v>56</v>
-      </c>
-      <c r="T14" t="s">
-        <v>57</v>
-      </c>
-      <c r="U14" t="s">
-        <v>34</v>
-      </c>
-      <c r="X14">
+      <c r="P14" t="s">
+        <v>52</v>
+      </c>
+      <c r="W14" t="s">
+        <v>34</v>
+      </c>
+      <c r="X14" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB14">
         <v>1</v>
       </c>
     </row>
@@ -1099,7 +1234,7 @@
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D15">
         <v>4</v>
@@ -1111,36 +1246,39 @@
         <v>6</v>
       </c>
       <c r="G15" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H15" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I15" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J15">
         <v>0</v>
       </c>
       <c r="K15" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L15">
         <v>8</v>
       </c>
-      <c r="R15" t="s">
-        <v>30</v>
-      </c>
-      <c r="S15" t="s">
-        <v>58</v>
-      </c>
-      <c r="T15" t="s">
-        <v>59</v>
-      </c>
-      <c r="U15" t="s">
-        <v>30</v>
-      </c>
-      <c r="X15">
+      <c r="P15" t="s">
+        <v>65</v>
+      </c>
+      <c r="W15" t="s">
+        <v>34</v>
+      </c>
+      <c r="X15" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB15">
         <v>1</v>
       </c>
     </row>
@@ -1152,7 +1290,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -1164,39 +1302,45 @@
         <v>-6</v>
       </c>
       <c r="G16" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H16" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I16" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J16">
         <v>-2</v>
       </c>
       <c r="K16" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L16">
         <v>6</v>
       </c>
       <c r="M16" t="s">
-        <v>61</v>
-      </c>
-      <c r="R16" t="s">
-        <v>34</v>
-      </c>
-      <c r="S16" t="s">
-        <v>35</v>
-      </c>
-      <c r="U16" t="s">
-        <v>30</v>
-      </c>
-      <c r="W16">
-        <v>6</v>
-      </c>
-      <c r="X16">
+        <v>69</v>
+      </c>
+      <c r="P16" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>71</v>
+      </c>
+      <c r="S16">
+        <v>6</v>
+      </c>
+      <c r="W16" t="s">
+        <v>39</v>
+      </c>
+      <c r="X16" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB16">
         <v>2</v>
       </c>
     </row>
@@ -1208,7 +1352,7 @@
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D17">
         <v>2</v>
@@ -1220,39 +1364,45 @@
         <v>-4</v>
       </c>
       <c r="G17" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H17" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I17" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J17">
         <v>2</v>
       </c>
       <c r="K17" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L17">
         <v>7</v>
       </c>
       <c r="M17" t="s">
-        <v>62</v>
-      </c>
-      <c r="R17" t="s">
-        <v>34</v>
-      </c>
-      <c r="S17" t="s">
-        <v>54</v>
-      </c>
-      <c r="U17" t="s">
-        <v>30</v>
-      </c>
-      <c r="W17">
-        <v>3</v>
-      </c>
-      <c r="X17">
+        <v>72</v>
+      </c>
+      <c r="P17" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>73</v>
+      </c>
+      <c r="S17">
+        <v>3</v>
+      </c>
+      <c r="W17" t="s">
+        <v>39</v>
+      </c>
+      <c r="X17" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB17">
         <v>2</v>
       </c>
     </row>
@@ -1264,7 +1414,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D18">
         <v>3</v>
@@ -1276,24 +1426,27 @@
         <v>-6</v>
       </c>
       <c r="G18" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I18" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="J18">
         <v>5</v>
       </c>
       <c r="K18" t="s">
-        <v>45</v>
-      </c>
-      <c r="R18" t="s">
-        <v>34</v>
-      </c>
-      <c r="S18" t="s">
-        <v>35</v>
-      </c>
-      <c r="X18">
+        <v>51</v>
+      </c>
+      <c r="P18" t="s">
+        <v>52</v>
+      </c>
+      <c r="W18" t="s">
+        <v>39</v>
+      </c>
+      <c r="X18" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB18">
         <v>2</v>
       </c>
     </row>
@@ -1305,7 +1458,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D19">
         <v>3</v>
@@ -1317,19 +1470,19 @@
         <v>-11</v>
       </c>
       <c r="G19" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H19" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I19" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J19">
         <v>0</v>
       </c>
       <c r="K19" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L19">
         <v>6</v>
@@ -1340,22 +1493,28 @@
       <c r="O19">
         <v>4</v>
       </c>
-      <c r="R19" t="s">
-        <v>34</v>
-      </c>
-      <c r="S19" t="s">
-        <v>54</v>
-      </c>
-      <c r="U19" t="s">
-        <v>30</v>
-      </c>
-      <c r="V19" t="s">
-        <v>34</v>
-      </c>
-      <c r="W19">
-        <v>6</v>
-      </c>
-      <c r="X19">
+      <c r="P19" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>71</v>
+      </c>
+      <c r="S19">
+        <v>6</v>
+      </c>
+      <c r="W19" t="s">
+        <v>39</v>
+      </c>
+      <c r="X19" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA19" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB19">
         <v>2</v>
       </c>
     </row>
@@ -1367,7 +1526,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D20">
         <v>4</v>
@@ -1379,18 +1538,18 @@
         <v>-11</v>
       </c>
       <c r="G20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H20" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="I20" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q20">
+        <v>76</v>
+      </c>
+      <c r="V20">
         <v>15</v>
       </c>
-      <c r="X20">
+      <c r="AB20">
         <v>2</v>
       </c>
     </row>
@@ -1402,7 +1561,7 @@
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -1414,36 +1573,39 @@
         <v>26</v>
       </c>
       <c r="G21" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H21" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I21" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J21">
         <v>6</v>
       </c>
       <c r="K21" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L21">
         <v>7</v>
       </c>
-      <c r="R21" t="s">
-        <v>34</v>
-      </c>
-      <c r="S21" t="s">
-        <v>39</v>
-      </c>
-      <c r="T21" t="s">
-        <v>66</v>
-      </c>
-      <c r="U21" t="s">
-        <v>30</v>
-      </c>
-      <c r="X21">
+      <c r="P21" t="s">
+        <v>38</v>
+      </c>
+      <c r="W21" t="s">
+        <v>39</v>
+      </c>
+      <c r="X21" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>77</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB21">
         <v>2</v>
       </c>
     </row>
@@ -1455,7 +1617,7 @@
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D22">
         <v>2</v>
@@ -1467,30 +1629,33 @@
         <v>20</v>
       </c>
       <c r="G22" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H22" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I22" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J22">
         <v>4</v>
       </c>
       <c r="K22" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L22">
         <v>7</v>
       </c>
-      <c r="T22" t="s">
-        <v>67</v>
-      </c>
-      <c r="U22" t="s">
-        <v>34</v>
-      </c>
-      <c r="X22">
+      <c r="P22" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>79</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB22">
         <v>2</v>
       </c>
     </row>
@@ -1502,7 +1667,7 @@
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D23">
         <v>1</v>
@@ -1514,36 +1679,39 @@
         <v>16</v>
       </c>
       <c r="G23" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H23" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I23" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J23">
         <v>6</v>
       </c>
       <c r="K23" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L23">
         <v>7</v>
       </c>
-      <c r="R23" t="s">
-        <v>49</v>
-      </c>
-      <c r="S23" t="s">
-        <v>50</v>
-      </c>
-      <c r="T23" t="s">
-        <v>51</v>
-      </c>
-      <c r="U23" t="s">
-        <v>30</v>
-      </c>
-      <c r="X23">
+      <c r="P23" t="s">
+        <v>47</v>
+      </c>
+      <c r="W23" t="s">
+        <v>56</v>
+      </c>
+      <c r="X23" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB23">
         <v>2</v>
       </c>
     </row>
@@ -1555,7 +1723,7 @@
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D24">
         <v>2</v>
@@ -1567,39 +1735,42 @@
         <v>10</v>
       </c>
       <c r="G24" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H24" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I24" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="J24">
         <v>10</v>
       </c>
       <c r="K24" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L24">
         <v>6</v>
       </c>
-      <c r="R24" t="s">
-        <v>34</v>
-      </c>
-      <c r="S24" t="s">
-        <v>54</v>
-      </c>
-      <c r="T24" t="s">
-        <v>69</v>
-      </c>
-      <c r="U24" t="s">
-        <v>30</v>
-      </c>
-      <c r="V24" t="s">
-        <v>34</v>
-      </c>
-      <c r="X24">
+      <c r="P24" t="s">
+        <v>38</v>
+      </c>
+      <c r="W24" t="s">
+        <v>39</v>
+      </c>
+      <c r="X24" t="s">
+        <v>61</v>
+      </c>
+      <c r="Y24" t="s">
+        <v>81</v>
+      </c>
+      <c r="Z24" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA24" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB24">
         <v>2</v>
       </c>
     </row>
@@ -1611,7 +1782,7 @@
         <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -1623,15 +1794,15 @@
         <v>3</v>
       </c>
       <c r="G25" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H25" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="I25" t="s">
-        <v>71</v>
-      </c>
-      <c r="X25">
+        <v>83</v>
+      </c>
+      <c r="AB25">
         <v>2</v>
       </c>
     </row>
@@ -1643,7 +1814,7 @@
         <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -1655,15 +1826,15 @@
         <v>-40</v>
       </c>
       <c r="G26" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H26" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="I26" t="s">
-        <v>28</v>
-      </c>
-      <c r="X26">
+        <v>32</v>
+      </c>
+      <c r="AB26">
         <v>3</v>
       </c>
     </row>
@@ -1675,7 +1846,7 @@
         <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D27">
         <v>1</v>
@@ -1687,39 +1858,45 @@
         <v>-20</v>
       </c>
       <c r="G27" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H27" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I27" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J27">
         <v>3</v>
       </c>
       <c r="K27" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L27">
         <v>6</v>
       </c>
       <c r="M27" t="s">
-        <v>73</v>
-      </c>
-      <c r="R27" t="s">
-        <v>34</v>
-      </c>
-      <c r="S27" t="s">
-        <v>54</v>
-      </c>
-      <c r="U27" t="s">
-        <v>34</v>
-      </c>
-      <c r="V27" t="s">
-        <v>30</v>
-      </c>
-      <c r="X27">
+        <v>85</v>
+      </c>
+      <c r="P27" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>86</v>
+      </c>
+      <c r="W27" t="s">
+        <v>39</v>
+      </c>
+      <c r="X27" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA27" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB27">
         <v>3</v>
       </c>
     </row>
@@ -1731,7 +1908,7 @@
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D28">
         <v>2</v>
@@ -1743,19 +1920,19 @@
         <v>-23</v>
       </c>
       <c r="G28" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H28" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I28" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J28">
         <v>0</v>
       </c>
       <c r="K28" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L28">
         <v>7</v>
@@ -1766,16 +1943,25 @@
       <c r="O28">
         <v>9</v>
       </c>
-      <c r="R28" t="s">
-        <v>34</v>
-      </c>
-      <c r="S28" t="s">
-        <v>74</v>
-      </c>
-      <c r="U28" t="s">
-        <v>34</v>
-      </c>
-      <c r="X28">
+      <c r="P28" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>71</v>
+      </c>
+      <c r="S28">
+        <v>6</v>
+      </c>
+      <c r="W28" t="s">
+        <v>39</v>
+      </c>
+      <c r="X28" t="s">
+        <v>87</v>
+      </c>
+      <c r="Z28" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB28">
         <v>3</v>
       </c>
     </row>
@@ -1787,7 +1973,7 @@
         <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D29">
         <v>3</v>
@@ -1799,39 +1985,45 @@
         <v>-23</v>
       </c>
       <c r="G29" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H29" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I29" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J29">
         <v>7</v>
       </c>
       <c r="K29" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L29">
         <v>7</v>
       </c>
-      <c r="R29" t="s">
-        <v>30</v>
+      <c r="P29" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>88</v>
       </c>
       <c r="S29" t="s">
-        <v>54</v>
-      </c>
-      <c r="U29" t="s">
-        <v>34</v>
-      </c>
-      <c r="V29" t="s">
-        <v>34</v>
+        <v>89</v>
       </c>
       <c r="W29" t="s">
-        <v>75</v>
-      </c>
-      <c r="X29">
+        <v>34</v>
+      </c>
+      <c r="X29" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA29" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB29">
         <v>3</v>
       </c>
     </row>
@@ -1843,7 +2035,7 @@
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D30">
         <v>1</v>
@@ -1855,19 +2047,19 @@
         <v>-30</v>
       </c>
       <c r="G30" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H30" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I30" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="J30">
         <v>16</v>
       </c>
       <c r="K30" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L30">
         <v>6</v>
@@ -1878,19 +2070,25 @@
       <c r="O30">
         <v>5</v>
       </c>
-      <c r="R30" t="s">
-        <v>30</v>
-      </c>
-      <c r="S30" t="s">
-        <v>54</v>
-      </c>
-      <c r="U30" t="s">
-        <v>30</v>
-      </c>
-      <c r="W30">
-        <v>3</v>
-      </c>
-      <c r="X30">
+      <c r="P30" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>71</v>
+      </c>
+      <c r="S30">
+        <v>3</v>
+      </c>
+      <c r="W30" t="s">
+        <v>34</v>
+      </c>
+      <c r="X30" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB30">
         <v>3</v>
       </c>
     </row>
@@ -1902,7 +2100,7 @@
         <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D31">
         <v>1</v>
@@ -1914,42 +2112,48 @@
         <v>-46</v>
       </c>
       <c r="G31" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H31" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I31" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J31">
         <v>-2</v>
       </c>
       <c r="K31" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L31">
         <v>6</v>
       </c>
       <c r="M31" t="s">
+        <v>69</v>
+      </c>
+      <c r="P31" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>86</v>
+      </c>
+      <c r="S31">
+        <v>3</v>
+      </c>
+      <c r="W31" t="s">
+        <v>34</v>
+      </c>
+      <c r="X31" t="s">
         <v>61</v>
       </c>
-      <c r="R31" t="s">
-        <v>30</v>
-      </c>
-      <c r="S31" t="s">
-        <v>54</v>
-      </c>
-      <c r="U31" t="s">
-        <v>30</v>
-      </c>
-      <c r="V31" t="s">
-        <v>34</v>
-      </c>
-      <c r="W31">
-        <v>3</v>
-      </c>
-      <c r="X31">
+      <c r="Z31" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA31" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB31">
         <v>3</v>
       </c>
     </row>
@@ -1961,7 +2165,7 @@
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D32">
         <v>2</v>
@@ -1973,19 +2177,19 @@
         <v>-44</v>
       </c>
       <c r="G32" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H32" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I32" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="J32">
         <v>56</v>
       </c>
       <c r="K32" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L32">
         <v>7</v>
@@ -1996,22 +2200,28 @@
       <c r="O32">
         <v>5</v>
       </c>
-      <c r="R32" t="s">
-        <v>30</v>
-      </c>
-      <c r="S32" t="s">
-        <v>74</v>
-      </c>
-      <c r="U32" t="s">
-        <v>30</v>
-      </c>
-      <c r="V32" t="s">
-        <v>30</v>
-      </c>
-      <c r="W32">
-        <v>3</v>
-      </c>
-      <c r="X32">
+      <c r="P32" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>71</v>
+      </c>
+      <c r="S32">
+        <v>3</v>
+      </c>
+      <c r="W32" t="s">
+        <v>34</v>
+      </c>
+      <c r="X32" t="s">
+        <v>87</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA32" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB32">
         <v>3</v>
       </c>
     </row>
@@ -2023,7 +2233,7 @@
         <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D33">
         <v>1</v>
@@ -2035,15 +2245,15 @@
         <v>3</v>
       </c>
       <c r="G33" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H33" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="I33" t="s">
-        <v>78</v>
-      </c>
-      <c r="X33">
+        <v>92</v>
+      </c>
+      <c r="AB33">
         <v>3</v>
       </c>
     </row>
@@ -2055,7 +2265,7 @@
         <v>1</v>
       </c>
       <c r="C34" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D34">
         <v>1</v>
@@ -2067,15 +2277,15 @@
         <v>-40</v>
       </c>
       <c r="G34" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H34" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I34" t="s">
-        <v>28</v>
-      </c>
-      <c r="X34">
+        <v>32</v>
+      </c>
+      <c r="AB34">
         <v>4</v>
       </c>
     </row>
@@ -2087,7 +2297,7 @@
         <v>1</v>
       </c>
       <c r="C35" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D35">
         <v>1</v>
@@ -2099,19 +2309,19 @@
         <v>-20</v>
       </c>
       <c r="G35" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H35" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I35" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="J35">
         <v>80</v>
       </c>
       <c r="K35" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L35">
         <v>7</v>
@@ -2122,19 +2332,22 @@
       <c r="O35">
         <v>2</v>
       </c>
-      <c r="R35" t="s">
-        <v>49</v>
-      </c>
-      <c r="S35" t="s">
-        <v>50</v>
-      </c>
-      <c r="T35" t="s">
-        <v>79</v>
-      </c>
-      <c r="U35" t="s">
-        <v>34</v>
-      </c>
-      <c r="X35">
+      <c r="P35" t="s">
+        <v>47</v>
+      </c>
+      <c r="W35" t="s">
+        <v>56</v>
+      </c>
+      <c r="X35" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y35" t="s">
+        <v>93</v>
+      </c>
+      <c r="Z35" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB35">
         <v>3</v>
       </c>
     </row>
@@ -2146,7 +2359,7 @@
         <v>1</v>
       </c>
       <c r="C36" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D36">
         <v>1</v>
@@ -2158,15 +2371,15 @@
         <v>3</v>
       </c>
       <c r="G36" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H36" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="I36" t="s">
-        <v>78</v>
-      </c>
-      <c r="X36">
+        <v>92</v>
+      </c>
+      <c r="AB36">
         <v>3</v>
       </c>
     </row>
@@ -2178,7 +2391,7 @@
         <v>1</v>
       </c>
       <c r="C37" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D37">
         <v>1</v>
@@ -2190,18 +2403,18 @@
         <v>-40</v>
       </c>
       <c r="G37" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H37" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="I37" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q37">
+        <v>76</v>
+      </c>
+      <c r="V37">
         <v>20</v>
       </c>
-      <c r="X37">
+      <c r="AB37">
         <v>4</v>
       </c>
     </row>
@@ -2213,7 +2426,7 @@
         <v>1</v>
       </c>
       <c r="C38" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D38">
         <v>1</v>
@@ -2225,39 +2438,45 @@
         <v>-21</v>
       </c>
       <c r="G38" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H38" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I38" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J38">
         <v>2</v>
       </c>
       <c r="K38" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L38">
         <v>7</v>
       </c>
       <c r="M38" t="s">
-        <v>61</v>
-      </c>
-      <c r="R38" t="s">
-        <v>30</v>
-      </c>
-      <c r="S38" t="s">
-        <v>47</v>
-      </c>
-      <c r="U38" t="s">
-        <v>30</v>
-      </c>
-      <c r="W38">
-        <v>6</v>
-      </c>
-      <c r="X38">
+        <v>69</v>
+      </c>
+      <c r="P38" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>94</v>
+      </c>
+      <c r="S38">
+        <v>6</v>
+      </c>
+      <c r="W38" t="s">
+        <v>34</v>
+      </c>
+      <c r="X38" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z38" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB38">
         <v>4</v>
       </c>
     </row>
@@ -2269,7 +2488,7 @@
         <v>1</v>
       </c>
       <c r="C39" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D39">
         <v>2</v>
@@ -2281,19 +2500,19 @@
         <v>-23</v>
       </c>
       <c r="G39" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H39" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I39" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="J39">
         <v>17</v>
       </c>
       <c r="K39" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L39">
         <v>7</v>
@@ -2304,19 +2523,28 @@
       <c r="O39">
         <v>2</v>
       </c>
+      <c r="P39" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>71</v>
+      </c>
       <c r="R39" t="s">
-        <v>34</v>
-      </c>
-      <c r="S39" t="s">
-        <v>54</v>
-      </c>
-      <c r="U39" t="s">
-        <v>34</v>
-      </c>
-      <c r="W39">
-        <v>3</v>
-      </c>
-      <c r="X39">
+        <v>86</v>
+      </c>
+      <c r="S39">
+        <v>3</v>
+      </c>
+      <c r="W39" t="s">
+        <v>39</v>
+      </c>
+      <c r="X39" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z39" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB39">
         <v>4</v>
       </c>
     </row>
@@ -2328,7 +2556,7 @@
         <v>1</v>
       </c>
       <c r="C40" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D40">
         <v>1</v>
@@ -2340,19 +2568,19 @@
         <v>-40</v>
       </c>
       <c r="G40" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H40" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I40" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J40">
         <v>0</v>
       </c>
       <c r="K40" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L40">
         <v>6</v>
@@ -2363,19 +2591,28 @@
       <c r="O40">
         <v>3</v>
       </c>
+      <c r="P40" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>71</v>
+      </c>
       <c r="R40" t="s">
-        <v>49</v>
-      </c>
-      <c r="S40" t="s">
-        <v>80</v>
-      </c>
-      <c r="U40" t="s">
-        <v>34</v>
-      </c>
-      <c r="W40">
-        <v>6</v>
-      </c>
-      <c r="X40">
+        <v>95</v>
+      </c>
+      <c r="S40">
+        <v>6</v>
+      </c>
+      <c r="W40" t="s">
+        <v>34</v>
+      </c>
+      <c r="X40" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z40" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB40">
         <v>4</v>
       </c>
     </row>
@@ -2387,7 +2624,7 @@
         <v>1</v>
       </c>
       <c r="C41" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D41">
         <v>2</v>
@@ -2399,19 +2636,19 @@
         <v>-40</v>
       </c>
       <c r="G41" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H41" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I41" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="J41">
         <v>0</v>
       </c>
       <c r="K41" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L41">
         <v>6</v>
@@ -2422,22 +2659,28 @@
       <c r="O41">
         <v>5</v>
       </c>
-      <c r="R41" t="s">
-        <v>30</v>
-      </c>
-      <c r="S41" t="s">
-        <v>54</v>
-      </c>
-      <c r="U41" t="s">
-        <v>30</v>
-      </c>
-      <c r="V41" t="s">
-        <v>34</v>
-      </c>
-      <c r="W41">
-        <v>3</v>
-      </c>
-      <c r="X41">
+      <c r="P41" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>71</v>
+      </c>
+      <c r="S41">
+        <v>3</v>
+      </c>
+      <c r="W41" t="s">
+        <v>34</v>
+      </c>
+      <c r="X41" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z41" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA41" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB41">
         <v>4</v>
       </c>
     </row>
@@ -2449,7 +2692,7 @@
         <v>1</v>
       </c>
       <c r="C42" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D42">
         <v>1</v>
@@ -2461,36 +2704,39 @@
         <v>-39</v>
       </c>
       <c r="G42" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H42" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I42" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="J42">
         <v>61</v>
       </c>
       <c r="K42" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L42">
         <v>7</v>
       </c>
-      <c r="R42" t="s">
-        <v>34</v>
-      </c>
-      <c r="S42" t="s">
-        <v>82</v>
-      </c>
-      <c r="T42" t="s">
-        <v>83</v>
-      </c>
-      <c r="U42" t="s">
-        <v>34</v>
-      </c>
-      <c r="X42">
+      <c r="P42" t="s">
+        <v>47</v>
+      </c>
+      <c r="W42" t="s">
+        <v>39</v>
+      </c>
+      <c r="X42" t="s">
+        <v>98</v>
+      </c>
+      <c r="Y42" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z42" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB42">
         <v>4</v>
       </c>
     </row>
@@ -2502,7 +2748,7 @@
         <v>1</v>
       </c>
       <c r="C43" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D43">
         <v>1</v>
@@ -2514,15 +2760,15 @@
         <v>3</v>
       </c>
       <c r="G43" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H43" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="I43" t="s">
-        <v>78</v>
-      </c>
-      <c r="X43">
+        <v>92</v>
+      </c>
+      <c r="AB43">
         <v>4</v>
       </c>
     </row>
@@ -2534,7 +2780,7 @@
         <v>1</v>
       </c>
       <c r="C44" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D44">
         <v>1</v>
@@ -2546,15 +2792,15 @@
         <v>-40</v>
       </c>
       <c r="G44" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H44" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="I44" t="s">
-        <v>28</v>
-      </c>
-      <c r="X44">
+        <v>32</v>
+      </c>
+      <c r="AB44">
         <v>5</v>
       </c>
     </row>
@@ -2566,7 +2812,7 @@
         <v>1</v>
       </c>
       <c r="C45" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D45">
         <v>1</v>
@@ -2578,39 +2824,45 @@
         <v>-20</v>
       </c>
       <c r="G45" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H45" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I45" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J45">
         <v>1</v>
       </c>
       <c r="K45" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L45">
         <v>6</v>
       </c>
       <c r="M45" t="s">
-        <v>73</v>
-      </c>
-      <c r="R45" t="s">
-        <v>34</v>
-      </c>
-      <c r="S45" t="s">
-        <v>54</v>
-      </c>
-      <c r="U45" t="s">
-        <v>34</v>
-      </c>
-      <c r="W45">
-        <v>3</v>
-      </c>
-      <c r="X45">
+        <v>85</v>
+      </c>
+      <c r="P45" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>71</v>
+      </c>
+      <c r="S45">
+        <v>3</v>
+      </c>
+      <c r="W45" t="s">
+        <v>39</v>
+      </c>
+      <c r="X45" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z45" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB45">
         <v>5</v>
       </c>
     </row>
@@ -2622,7 +2874,7 @@
         <v>2</v>
       </c>
       <c r="C46" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D46">
         <v>2</v>
@@ -2634,19 +2886,19 @@
         <v>-21</v>
       </c>
       <c r="G46" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H46" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I46" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="J46">
         <v>7</v>
       </c>
       <c r="K46" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L46">
         <v>7</v>
@@ -2657,19 +2909,28 @@
       <c r="O46">
         <v>2</v>
       </c>
+      <c r="P46" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>71</v>
+      </c>
       <c r="R46" t="s">
-        <v>34</v>
-      </c>
-      <c r="S46" t="s">
-        <v>74</v>
-      </c>
-      <c r="U46" t="s">
-        <v>34</v>
-      </c>
-      <c r="W46">
-        <v>3</v>
-      </c>
-      <c r="X46">
+        <v>73</v>
+      </c>
+      <c r="S46">
+        <v>3</v>
+      </c>
+      <c r="W46" t="s">
+        <v>39</v>
+      </c>
+      <c r="X46" t="s">
+        <v>87</v>
+      </c>
+      <c r="Z46" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB46">
         <v>5</v>
       </c>
     </row>
@@ -2681,7 +2942,7 @@
         <v>2</v>
       </c>
       <c r="C47" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D47">
         <v>3</v>
@@ -2693,19 +2954,19 @@
         <v>-28</v>
       </c>
       <c r="G47" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H47" t="s">
+        <v>42</v>
+      </c>
+      <c r="I47" t="s">
+        <v>60</v>
+      </c>
+      <c r="J47">
+        <v>6</v>
+      </c>
+      <c r="K47" t="s">
         <v>37</v>
-      </c>
-      <c r="I47" t="s">
-        <v>53</v>
-      </c>
-      <c r="J47">
-        <v>6</v>
-      </c>
-      <c r="K47" t="s">
-        <v>33</v>
       </c>
       <c r="L47">
         <v>7</v>
@@ -2716,19 +2977,25 @@
       <c r="O47">
         <v>2</v>
       </c>
-      <c r="R47" t="s">
-        <v>30</v>
-      </c>
-      <c r="S47" t="s">
-        <v>84</v>
-      </c>
-      <c r="U47" t="s">
-        <v>30</v>
-      </c>
-      <c r="W47">
-        <v>3</v>
-      </c>
-      <c r="X47">
+      <c r="P47" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>71</v>
+      </c>
+      <c r="S47">
+        <v>3</v>
+      </c>
+      <c r="W47" t="s">
+        <v>34</v>
+      </c>
+      <c r="X47" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z47" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB47">
         <v>5</v>
       </c>
     </row>
@@ -2740,7 +3007,7 @@
         <v>2</v>
       </c>
       <c r="C48" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D48">
         <v>1</v>
@@ -2752,36 +3019,39 @@
         <v>-34</v>
       </c>
       <c r="G48" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H48" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I48" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="J48">
         <v>-5</v>
       </c>
       <c r="K48" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L48">
         <v>6</v>
       </c>
-      <c r="R48" t="s">
-        <v>34</v>
-      </c>
-      <c r="S48" t="s">
-        <v>54</v>
-      </c>
-      <c r="U48" t="s">
-        <v>30</v>
-      </c>
-      <c r="V48" t="s">
-        <v>30</v>
-      </c>
-      <c r="X48">
+      <c r="P48" t="s">
+        <v>38</v>
+      </c>
+      <c r="W48" t="s">
+        <v>39</v>
+      </c>
+      <c r="X48" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z48" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA48" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB48">
         <v>5</v>
       </c>
     </row>
@@ -2793,7 +3063,7 @@
         <v>2</v>
       </c>
       <c r="C49" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D49">
         <v>1</v>
@@ -2805,36 +3075,42 @@
         <v>-29</v>
       </c>
       <c r="G49" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H49" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I49" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="J49">
         <v>-3</v>
       </c>
       <c r="K49" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L49">
         <v>6</v>
       </c>
-      <c r="R49" t="s">
-        <v>34</v>
-      </c>
-      <c r="S49" t="s">
-        <v>54</v>
-      </c>
-      <c r="U49" t="s">
-        <v>30</v>
-      </c>
-      <c r="W49">
-        <v>3</v>
-      </c>
-      <c r="X49">
+      <c r="P49" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>71</v>
+      </c>
+      <c r="S49">
+        <v>3</v>
+      </c>
+      <c r="W49" t="s">
+        <v>39</v>
+      </c>
+      <c r="X49" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z49" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB49">
         <v>5</v>
       </c>
     </row>
@@ -2846,7 +3122,7 @@
         <v>2</v>
       </c>
       <c r="C50" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D50">
         <v>2</v>
@@ -2858,42 +3134,48 @@
         <v>-26</v>
       </c>
       <c r="G50" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H50" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I50" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J50">
         <v>-2</v>
       </c>
       <c r="K50" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L50">
         <v>6</v>
       </c>
       <c r="M50" t="s">
-        <v>61</v>
-      </c>
-      <c r="R50" t="s">
-        <v>49</v>
-      </c>
-      <c r="S50" t="s">
-        <v>80</v>
-      </c>
-      <c r="U50" t="s">
-        <v>34</v>
-      </c>
-      <c r="V50" t="s">
-        <v>34</v>
-      </c>
-      <c r="W50">
-        <v>6</v>
-      </c>
-      <c r="X50">
+        <v>69</v>
+      </c>
+      <c r="P50" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>103</v>
+      </c>
+      <c r="S50">
+        <v>6</v>
+      </c>
+      <c r="W50" t="s">
+        <v>56</v>
+      </c>
+      <c r="X50" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z50" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA50" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB50">
         <v>5</v>
       </c>
     </row>
@@ -2905,7 +3187,7 @@
         <v>2</v>
       </c>
       <c r="C51" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D51">
         <v>3</v>
@@ -2917,19 +3199,19 @@
         <v>-24</v>
       </c>
       <c r="G51" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H51" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I51" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="J51">
         <v>76</v>
       </c>
       <c r="K51" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L51">
         <v>6</v>
@@ -2940,19 +3222,28 @@
       <c r="O51">
         <v>7</v>
       </c>
+      <c r="P51" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>71</v>
+      </c>
       <c r="R51" t="s">
-        <v>49</v>
-      </c>
-      <c r="S51" t="s">
-        <v>80</v>
-      </c>
-      <c r="U51" t="s">
-        <v>30</v>
-      </c>
-      <c r="W51">
-        <v>6</v>
-      </c>
-      <c r="X51">
+        <v>104</v>
+      </c>
+      <c r="S51">
+        <v>6</v>
+      </c>
+      <c r="W51" t="s">
+        <v>39</v>
+      </c>
+      <c r="X51" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z51" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB51">
         <v>5</v>
       </c>
     </row>
@@ -2964,7 +3255,7 @@
         <v>2</v>
       </c>
       <c r="C52" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D52">
         <v>1</v>
@@ -2976,15 +3267,15 @@
         <v>3</v>
       </c>
       <c r="G52" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H52" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="I52" t="s">
-        <v>78</v>
-      </c>
-      <c r="X52">
+        <v>92</v>
+      </c>
+      <c r="AB52">
         <v>5</v>
       </c>
     </row>
@@ -2996,7 +3287,7 @@
         <v>2</v>
       </c>
       <c r="C53" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D53">
         <v>1</v>
@@ -3008,15 +3299,15 @@
         <v>-40</v>
       </c>
       <c r="G53" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H53" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I53" t="s">
-        <v>28</v>
-      </c>
-      <c r="X53">
+        <v>32</v>
+      </c>
+      <c r="AB53">
         <v>6</v>
       </c>
     </row>
@@ -3028,7 +3319,7 @@
         <v>2</v>
       </c>
       <c r="C54" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -3040,39 +3331,42 @@
         <v>-20</v>
       </c>
       <c r="G54" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H54" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I54" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J54">
         <v>5</v>
       </c>
       <c r="K54" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L54">
         <v>6</v>
       </c>
-      <c r="R54" t="s">
-        <v>34</v>
-      </c>
-      <c r="S54" t="s">
-        <v>39</v>
-      </c>
-      <c r="T54" t="s">
-        <v>86</v>
-      </c>
-      <c r="U54" t="s">
-        <v>34</v>
-      </c>
-      <c r="V54" t="s">
-        <v>34</v>
-      </c>
-      <c r="X54">
+      <c r="P54" t="s">
+        <v>52</v>
+      </c>
+      <c r="W54" t="s">
+        <v>39</v>
+      </c>
+      <c r="X54" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y54" t="s">
+        <v>105</v>
+      </c>
+      <c r="Z54" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA54" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB54">
         <v>5</v>
       </c>
     </row>
@@ -3084,7 +3378,7 @@
         <v>2</v>
       </c>
       <c r="C55" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D55">
         <v>2</v>
@@ -3096,36 +3390,39 @@
         <v>-25</v>
       </c>
       <c r="G55" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H55" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I55" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J55">
         <v>8</v>
       </c>
       <c r="K55" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L55">
         <v>7</v>
       </c>
-      <c r="R55" t="s">
-        <v>49</v>
-      </c>
-      <c r="S55" t="s">
-        <v>50</v>
-      </c>
-      <c r="T55" t="s">
-        <v>79</v>
-      </c>
-      <c r="U55" t="s">
-        <v>30</v>
-      </c>
-      <c r="X55">
+      <c r="P55" t="s">
+        <v>47</v>
+      </c>
+      <c r="W55" t="s">
+        <v>56</v>
+      </c>
+      <c r="X55" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y55" t="s">
+        <v>93</v>
+      </c>
+      <c r="Z55" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB55">
         <v>5</v>
       </c>
     </row>
@@ -3137,7 +3434,7 @@
         <v>2</v>
       </c>
       <c r="C56" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D56">
         <v>1</v>
@@ -3149,36 +3446,39 @@
         <v>-33</v>
       </c>
       <c r="G56" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H56" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I56" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J56">
         <v>-1</v>
       </c>
       <c r="K56" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L56">
         <v>6</v>
       </c>
-      <c r="R56" t="s">
-        <v>34</v>
-      </c>
-      <c r="S56" t="s">
-        <v>82</v>
-      </c>
-      <c r="T56" t="s">
-        <v>83</v>
-      </c>
-      <c r="U56" t="s">
-        <v>30</v>
-      </c>
-      <c r="X56">
+      <c r="P56" t="s">
+        <v>47</v>
+      </c>
+      <c r="W56" t="s">
+        <v>39</v>
+      </c>
+      <c r="X56" t="s">
+        <v>98</v>
+      </c>
+      <c r="Y56" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z56" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB56">
         <v>5</v>
       </c>
     </row>
@@ -3190,7 +3490,7 @@
         <v>2</v>
       </c>
       <c r="C57" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D57">
         <v>2</v>
@@ -3202,19 +3502,19 @@
         <v>-32</v>
       </c>
       <c r="G57" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H57" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I57" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J57">
         <v>0</v>
       </c>
       <c r="K57" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L57">
         <v>6</v>
@@ -3225,19 +3525,22 @@
       <c r="O57">
         <v>6</v>
       </c>
-      <c r="R57" t="s">
-        <v>34</v>
-      </c>
-      <c r="S57" t="s">
-        <v>39</v>
-      </c>
-      <c r="T57" t="s">
-        <v>40</v>
-      </c>
-      <c r="U57" t="s">
-        <v>34</v>
-      </c>
-      <c r="X57">
+      <c r="P57" t="s">
+        <v>38</v>
+      </c>
+      <c r="W57" t="s">
+        <v>39</v>
+      </c>
+      <c r="X57" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y57" t="s">
+        <v>45</v>
+      </c>
+      <c r="Z57" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB57">
         <v>5</v>
       </c>
     </row>
@@ -3249,7 +3552,7 @@
         <v>2</v>
       </c>
       <c r="C58" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D58">
         <v>3</v>
@@ -3261,39 +3564,42 @@
         <v>-32</v>
       </c>
       <c r="G58" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H58" t="s">
+        <v>42</v>
+      </c>
+      <c r="I58" t="s">
+        <v>46</v>
+      </c>
+      <c r="J58">
+        <v>1</v>
+      </c>
+      <c r="K58" t="s">
         <v>37</v>
-      </c>
-      <c r="I58" t="s">
-        <v>41</v>
-      </c>
-      <c r="J58">
-        <v>1</v>
-      </c>
-      <c r="K58" t="s">
-        <v>33</v>
       </c>
       <c r="L58">
         <v>5</v>
       </c>
-      <c r="R58" t="s">
-        <v>34</v>
-      </c>
-      <c r="S58" t="s">
-        <v>35</v>
-      </c>
-      <c r="T58" t="s">
-        <v>87</v>
-      </c>
-      <c r="U58" t="s">
-        <v>34</v>
-      </c>
-      <c r="V58" t="s">
-        <v>34</v>
-      </c>
-      <c r="X58">
+      <c r="P58" t="s">
+        <v>38</v>
+      </c>
+      <c r="W58" t="s">
+        <v>39</v>
+      </c>
+      <c r="X58" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y58" t="s">
+        <v>106</v>
+      </c>
+      <c r="Z58" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA58" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB58">
         <v>5</v>
       </c>
     </row>
@@ -3305,7 +3611,7 @@
         <v>2</v>
       </c>
       <c r="C59" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D59">
         <v>4</v>
@@ -3317,15 +3623,15 @@
         <v>-33</v>
       </c>
       <c r="G59" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H59" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I59" t="s">
-        <v>88</v>
-      </c>
-      <c r="X59">
+        <v>107</v>
+      </c>
+      <c r="AB59">
         <v>5</v>
       </c>
     </row>
@@ -3337,7 +3643,7 @@
         <v>2</v>
       </c>
       <c r="C60" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D60">
         <v>1</v>
@@ -3349,45 +3655,51 @@
         <v>-16</v>
       </c>
       <c r="G60" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H60" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I60" t="s">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="J60">
         <v>84</v>
       </c>
       <c r="K60" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L60">
         <v>6</v>
       </c>
       <c r="M60" t="s">
-        <v>73</v>
-      </c>
-      <c r="Q60">
+        <v>85</v>
+      </c>
+      <c r="P60" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>71</v>
+      </c>
+      <c r="S60">
+        <v>3</v>
+      </c>
+      <c r="V60">
         <v>0</v>
       </c>
-      <c r="R60" t="s">
-        <v>34</v>
-      </c>
-      <c r="S60" t="s">
-        <v>54</v>
-      </c>
-      <c r="U60" t="s">
-        <v>30</v>
-      </c>
-      <c r="V60" t="s">
-        <v>30</v>
-      </c>
-      <c r="W60">
-        <v>3</v>
-      </c>
-      <c r="X60">
+      <c r="W60" t="s">
+        <v>39</v>
+      </c>
+      <c r="X60" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z60" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA60" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB60">
         <v>6</v>
       </c>
     </row>
@@ -3399,7 +3711,7 @@
         <v>2</v>
       </c>
       <c r="C61" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -3411,15 +3723,15 @@
         <v>3</v>
       </c>
       <c r="G61" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H61" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="I61" t="s">
-        <v>78</v>
-      </c>
-      <c r="X61">
+        <v>92</v>
+      </c>
+      <c r="AB61">
         <v>6</v>
       </c>
     </row>
@@ -3431,7 +3743,7 @@
         <v>2</v>
       </c>
       <c r="C62" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D62">
         <v>1</v>
@@ -3443,15 +3755,15 @@
         <v>-40</v>
       </c>
       <c r="G62" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H62" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I62" t="s">
-        <v>28</v>
-      </c>
-      <c r="X62">
+        <v>32</v>
+      </c>
+      <c r="AB62">
         <v>7</v>
       </c>
     </row>
@@ -3463,7 +3775,7 @@
         <v>2</v>
       </c>
       <c r="C63" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D63">
         <v>1</v>
@@ -3475,39 +3787,42 @@
         <v>-20</v>
       </c>
       <c r="G63" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H63" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I63" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J63">
         <v>4</v>
       </c>
       <c r="K63" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L63">
         <v>7</v>
       </c>
-      <c r="R63" t="s">
-        <v>30</v>
-      </c>
-      <c r="S63" t="s">
-        <v>74</v>
-      </c>
-      <c r="T63" t="s">
-        <v>89</v>
-      </c>
-      <c r="U63" t="s">
-        <v>34</v>
-      </c>
-      <c r="V63" t="s">
-        <v>34</v>
-      </c>
-      <c r="X63">
+      <c r="P63" t="s">
+        <v>47</v>
+      </c>
+      <c r="W63" t="s">
+        <v>34</v>
+      </c>
+      <c r="X63" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y63" t="s">
+        <v>108</v>
+      </c>
+      <c r="Z63" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA63" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB63">
         <v>6</v>
       </c>
     </row>
@@ -3519,7 +3834,7 @@
         <v>2</v>
       </c>
       <c r="C64" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D64">
         <v>2</v>
@@ -3531,36 +3846,39 @@
         <v>-24</v>
       </c>
       <c r="G64" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H64" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I64" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J64">
         <v>5</v>
       </c>
       <c r="K64" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L64">
         <v>5</v>
       </c>
-      <c r="R64" t="s">
-        <v>34</v>
-      </c>
-      <c r="S64" t="s">
-        <v>35</v>
-      </c>
-      <c r="T64" t="s">
-        <v>90</v>
-      </c>
-      <c r="U64" t="s">
-        <v>30</v>
-      </c>
-      <c r="X64">
+      <c r="P64" t="s">
+        <v>52</v>
+      </c>
+      <c r="W64" t="s">
+        <v>39</v>
+      </c>
+      <c r="X64" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y64" t="s">
+        <v>109</v>
+      </c>
+      <c r="Z64" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB64">
         <v>6</v>
       </c>
     </row>
@@ -3572,7 +3890,7 @@
         <v>2</v>
       </c>
       <c r="C65" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D65">
         <v>3</v>
@@ -3584,39 +3902,42 @@
         <v>-29</v>
       </c>
       <c r="G65" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H65" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I65" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J65">
         <v>8</v>
       </c>
       <c r="K65" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L65">
         <v>6</v>
       </c>
-      <c r="R65" t="s">
-        <v>34</v>
-      </c>
-      <c r="S65" t="s">
-        <v>47</v>
-      </c>
-      <c r="T65" t="s">
-        <v>48</v>
-      </c>
-      <c r="U65" t="s">
-        <v>34</v>
-      </c>
-      <c r="V65" t="s">
-        <v>30</v>
-      </c>
-      <c r="X65">
+      <c r="P65" t="s">
+        <v>70</v>
+      </c>
+      <c r="W65" t="s">
+        <v>39</v>
+      </c>
+      <c r="X65" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y65" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z65" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA65" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB65">
         <v>6</v>
       </c>
     </row>
@@ -3628,7 +3949,7 @@
         <v>2</v>
       </c>
       <c r="C66" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D66">
         <v>1</v>
@@ -3640,39 +3961,42 @@
         <v>-37</v>
       </c>
       <c r="G66" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H66" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I66" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J66">
         <v>0</v>
       </c>
       <c r="K66" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L66">
         <v>7</v>
       </c>
-      <c r="R66" t="s">
-        <v>30</v>
-      </c>
-      <c r="S66" t="s">
-        <v>91</v>
-      </c>
-      <c r="T66" t="s">
-        <v>89</v>
-      </c>
-      <c r="U66" t="s">
-        <v>34</v>
-      </c>
-      <c r="V66" t="s">
-        <v>34</v>
-      </c>
-      <c r="X66">
+      <c r="P66" t="s">
+        <v>110</v>
+      </c>
+      <c r="W66" t="s">
+        <v>34</v>
+      </c>
+      <c r="X66" t="s">
+        <v>111</v>
+      </c>
+      <c r="Y66" t="s">
+        <v>108</v>
+      </c>
+      <c r="Z66" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA66" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB66">
         <v>6</v>
       </c>
     </row>
@@ -3684,7 +4008,7 @@
         <v>2</v>
       </c>
       <c r="C67" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D67">
         <v>2</v>
@@ -3696,36 +4020,39 @@
         <v>-37</v>
       </c>
       <c r="G67" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H67" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I67" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J67">
         <v>-4</v>
       </c>
       <c r="K67" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L67">
         <v>6</v>
       </c>
-      <c r="R67" t="s">
-        <v>34</v>
-      </c>
-      <c r="S67" t="s">
-        <v>35</v>
-      </c>
-      <c r="T67" t="s">
-        <v>36</v>
-      </c>
-      <c r="U67" t="s">
-        <v>34</v>
-      </c>
-      <c r="X67">
+      <c r="P67" t="s">
+        <v>52</v>
+      </c>
+      <c r="W67" t="s">
+        <v>39</v>
+      </c>
+      <c r="X67" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y67" t="s">
+        <v>41</v>
+      </c>
+      <c r="Z67" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB67">
         <v>6</v>
       </c>
     </row>
@@ -3737,7 +4064,7 @@
         <v>2</v>
       </c>
       <c r="C68" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D68">
         <v>3</v>
@@ -3749,19 +4076,19 @@
         <v>-33</v>
       </c>
       <c r="G68" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H68" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I68" t="s">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="J68">
         <v>57</v>
       </c>
       <c r="K68" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L68">
         <v>6</v>
@@ -3772,19 +4099,22 @@
       <c r="O68">
         <v>5</v>
       </c>
-      <c r="R68" t="s">
-        <v>34</v>
-      </c>
-      <c r="S68" t="s">
-        <v>47</v>
-      </c>
-      <c r="T68" t="s">
-        <v>55</v>
-      </c>
-      <c r="U68" t="s">
-        <v>30</v>
-      </c>
-      <c r="X68">
+      <c r="P68" t="s">
+        <v>29</v>
+      </c>
+      <c r="W68" t="s">
+        <v>39</v>
+      </c>
+      <c r="X68" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y68" t="s">
+        <v>62</v>
+      </c>
+      <c r="Z68" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB68">
         <v>6</v>
       </c>
     </row>
@@ -3796,7 +4126,7 @@
         <v>2</v>
       </c>
       <c r="C69" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D69">
         <v>1</v>
@@ -3808,39 +4138,45 @@
         <v>-1</v>
       </c>
       <c r="G69" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H69" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I69" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J69">
         <v>1</v>
       </c>
       <c r="K69" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L69">
         <v>8</v>
       </c>
       <c r="M69" t="s">
-        <v>61</v>
-      </c>
-      <c r="R69" t="s">
-        <v>34</v>
-      </c>
-      <c r="S69" t="s">
-        <v>74</v>
-      </c>
-      <c r="U69" t="s">
-        <v>34</v>
-      </c>
-      <c r="W69">
-        <v>3</v>
-      </c>
-      <c r="X69">
+        <v>69</v>
+      </c>
+      <c r="P69" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>71</v>
+      </c>
+      <c r="S69">
+        <v>3</v>
+      </c>
+      <c r="W69" t="s">
+        <v>39</v>
+      </c>
+      <c r="X69" t="s">
+        <v>87</v>
+      </c>
+      <c r="Z69" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB69">
         <v>7</v>
       </c>
     </row>
@@ -3852,7 +4188,7 @@
         <v>2</v>
       </c>
       <c r="C70" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D70">
         <v>2</v>
@@ -3864,42 +4200,48 @@
         <v>-2</v>
       </c>
       <c r="G70" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H70" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I70" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J70">
         <v>2</v>
       </c>
       <c r="K70" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L70">
         <v>7</v>
       </c>
       <c r="M70" t="s">
-        <v>93</v>
-      </c>
-      <c r="R70" t="s">
-        <v>34</v>
-      </c>
-      <c r="S70" t="s">
-        <v>94</v>
-      </c>
-      <c r="U70" t="s">
-        <v>34</v>
-      </c>
-      <c r="V70" t="s">
-        <v>30</v>
-      </c>
-      <c r="W70">
-        <v>3</v>
-      </c>
-      <c r="X70">
+        <v>113</v>
+      </c>
+      <c r="P70" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>95</v>
+      </c>
+      <c r="S70">
+        <v>3</v>
+      </c>
+      <c r="W70" t="s">
+        <v>39</v>
+      </c>
+      <c r="X70" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z70" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA70" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB70">
         <v>7</v>
       </c>
     </row>
@@ -3911,7 +4253,7 @@
         <v>2</v>
       </c>
       <c r="C71" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D71">
         <v>3</v>
@@ -3923,19 +4265,19 @@
         <v>-4</v>
       </c>
       <c r="G71" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H71" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I71" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J71">
         <v>0</v>
       </c>
       <c r="K71" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L71">
         <v>7</v>
@@ -3946,19 +4288,25 @@
       <c r="O71">
         <v>8</v>
       </c>
-      <c r="R71" t="s">
-        <v>30</v>
-      </c>
-      <c r="S71" t="s">
-        <v>74</v>
-      </c>
-      <c r="U71" t="s">
-        <v>30</v>
-      </c>
-      <c r="W71">
-        <v>3</v>
-      </c>
-      <c r="X71">
+      <c r="P71" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>71</v>
+      </c>
+      <c r="S71">
+        <v>3</v>
+      </c>
+      <c r="W71" t="s">
+        <v>34</v>
+      </c>
+      <c r="X71" t="s">
+        <v>87</v>
+      </c>
+      <c r="Z71" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB71">
         <v>7</v>
       </c>
     </row>
@@ -3970,7 +4318,7 @@
         <v>2</v>
       </c>
       <c r="C72" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D72">
         <v>4</v>
@@ -3982,15 +4330,15 @@
         <v>-4</v>
       </c>
       <c r="G72" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H72" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="I72" t="s">
-        <v>95</v>
-      </c>
-      <c r="X72">
+        <v>115</v>
+      </c>
+      <c r="AB72">
         <v>7</v>
       </c>
     </row>
@@ -4002,7 +4350,7 @@
         <v>2</v>
       </c>
       <c r="C73" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D73">
         <v>1</v>
@@ -4014,19 +4362,19 @@
         <v>-20</v>
       </c>
       <c r="G73" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H73" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I73" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="J73">
         <v>13</v>
       </c>
       <c r="K73" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L73">
         <v>7</v>
@@ -4037,19 +4385,22 @@
       <c r="O73">
         <v>3</v>
       </c>
-      <c r="R73" t="s">
-        <v>34</v>
-      </c>
-      <c r="S73" t="s">
-        <v>82</v>
-      </c>
-      <c r="T73" t="s">
-        <v>96</v>
-      </c>
-      <c r="U73" t="s">
-        <v>34</v>
-      </c>
-      <c r="X73">
+      <c r="P73" t="s">
+        <v>52</v>
+      </c>
+      <c r="W73" t="s">
+        <v>39</v>
+      </c>
+      <c r="X73" t="s">
+        <v>98</v>
+      </c>
+      <c r="Y73" t="s">
+        <v>116</v>
+      </c>
+      <c r="Z73" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB73">
         <v>7</v>
       </c>
     </row>
@@ -4061,7 +4412,7 @@
         <v>2</v>
       </c>
       <c r="C74" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D74">
         <v>1</v>
@@ -4073,39 +4424,42 @@
         <v>-32</v>
       </c>
       <c r="G74" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H74" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I74" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J74">
         <v>2</v>
       </c>
       <c r="K74" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L74">
         <v>6</v>
       </c>
-      <c r="R74" t="s">
-        <v>30</v>
-      </c>
-      <c r="S74" t="s">
-        <v>47</v>
-      </c>
-      <c r="T74" t="s">
-        <v>48</v>
-      </c>
-      <c r="U74" t="s">
-        <v>30</v>
-      </c>
-      <c r="V74" t="s">
-        <v>30</v>
-      </c>
-      <c r="X74">
+      <c r="P74" t="s">
+        <v>52</v>
+      </c>
+      <c r="W74" t="s">
+        <v>34</v>
+      </c>
+      <c r="X74" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y74" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z74" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA74" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB74">
         <v>7</v>
       </c>
     </row>
@@ -4117,7 +4471,7 @@
         <v>2</v>
       </c>
       <c r="C75" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D75">
         <v>2</v>
@@ -4129,36 +4483,39 @@
         <v>-34</v>
       </c>
       <c r="G75" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H75" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I75" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J75">
         <v>1</v>
       </c>
       <c r="K75" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L75">
         <v>6</v>
       </c>
-      <c r="R75" t="s">
-        <v>30</v>
-      </c>
-      <c r="S75" t="s">
-        <v>39</v>
-      </c>
-      <c r="T75" t="s">
-        <v>97</v>
-      </c>
-      <c r="U75" t="s">
-        <v>30</v>
-      </c>
-      <c r="X75">
+      <c r="P75" t="s">
+        <v>47</v>
+      </c>
+      <c r="W75" t="s">
+        <v>34</v>
+      </c>
+      <c r="X75" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y75" t="s">
+        <v>117</v>
+      </c>
+      <c r="Z75" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB75">
         <v>7</v>
       </c>
     </row>
@@ -4170,7 +4527,7 @@
         <v>2</v>
       </c>
       <c r="C76" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D76">
         <v>3</v>
@@ -4182,39 +4539,42 @@
         <v>-35</v>
       </c>
       <c r="G76" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H76" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I76" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J76">
         <v>25</v>
       </c>
       <c r="K76" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L76">
         <v>3</v>
       </c>
-      <c r="R76" t="s">
-        <v>30</v>
-      </c>
-      <c r="S76" t="s">
-        <v>35</v>
-      </c>
-      <c r="T76" t="s">
-        <v>98</v>
-      </c>
-      <c r="U76" t="s">
-        <v>34</v>
-      </c>
-      <c r="V76" t="s">
-        <v>30</v>
-      </c>
-      <c r="X76">
+      <c r="P76" t="s">
+        <v>38</v>
+      </c>
+      <c r="W76" t="s">
+        <v>34</v>
+      </c>
+      <c r="X76" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y76" t="s">
+        <v>118</v>
+      </c>
+      <c r="Z76" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA76" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB76">
         <v>7</v>
       </c>
     </row>
@@ -4226,7 +4586,7 @@
         <v>2</v>
       </c>
       <c r="C77" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D77">
         <v>1</v>
@@ -4238,15 +4598,15 @@
         <v>40</v>
       </c>
       <c r="G77" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H77" t="s">
-        <v>99</v>
+        <v>119</v>
       </c>
       <c r="I77" t="s">
-        <v>71</v>
-      </c>
-      <c r="X77">
+        <v>83</v>
+      </c>
+      <c r="AB77">
         <v>7</v>
       </c>
     </row>
@@ -4258,7 +4618,7 @@
         <v>3</v>
       </c>
       <c r="C78" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D78">
         <v>1</v>
@@ -4270,15 +4630,15 @@
         <v>-40</v>
       </c>
       <c r="G78" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H78" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="I78" t="s">
-        <v>28</v>
-      </c>
-      <c r="X78">
+        <v>32</v>
+      </c>
+      <c r="AB78">
         <v>7</v>
       </c>
     </row>
@@ -4290,7 +4650,7 @@
         <v>3</v>
       </c>
       <c r="C79" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D79">
         <v>1</v>
@@ -4302,19 +4662,19 @@
         <v>-20</v>
       </c>
       <c r="G79" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H79" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I79" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="J79">
         <v>13</v>
       </c>
       <c r="K79" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L79">
         <v>7</v>
@@ -4325,19 +4685,28 @@
       <c r="O79">
         <v>4</v>
       </c>
-      <c r="R79" t="s">
-        <v>34</v>
-      </c>
-      <c r="S79" t="s">
-        <v>54</v>
-      </c>
-      <c r="U79" t="s">
-        <v>34</v>
-      </c>
-      <c r="V79" t="s">
-        <v>34</v>
-      </c>
-      <c r="X79">
+      <c r="P79" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>71</v>
+      </c>
+      <c r="S79">
+        <v>3</v>
+      </c>
+      <c r="W79" t="s">
+        <v>39</v>
+      </c>
+      <c r="X79" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z79" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA79" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB79">
         <v>7</v>
       </c>
     </row>
@@ -4349,7 +4718,7 @@
         <v>3</v>
       </c>
       <c r="C80" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D80">
         <v>1</v>
@@ -4361,42 +4730,48 @@
         <v>-33</v>
       </c>
       <c r="G80" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H80" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I80" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J80">
         <v>5</v>
       </c>
       <c r="K80" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L80">
         <v>7</v>
       </c>
       <c r="M80" t="s">
-        <v>62</v>
-      </c>
-      <c r="R80" t="s">
-        <v>49</v>
-      </c>
-      <c r="S80" t="s">
-        <v>80</v>
-      </c>
-      <c r="U80" t="s">
-        <v>34</v>
-      </c>
-      <c r="V80" t="s">
-        <v>34</v>
-      </c>
-      <c r="W80">
-        <v>6</v>
-      </c>
-      <c r="X80">
+        <v>72</v>
+      </c>
+      <c r="P80" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>95</v>
+      </c>
+      <c r="S80">
+        <v>6</v>
+      </c>
+      <c r="W80" t="s">
+        <v>56</v>
+      </c>
+      <c r="X80" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z80" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA80" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB80">
         <v>7</v>
       </c>
     </row>
@@ -4408,7 +4783,7 @@
         <v>3</v>
       </c>
       <c r="C81" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D81">
         <v>2</v>
@@ -4420,18 +4795,18 @@
         <v>-38</v>
       </c>
       <c r="G81" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I81" t="s">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="J81">
         <v>0</v>
       </c>
       <c r="K81" t="s">
-        <v>45</v>
-      </c>
-      <c r="X81">
+        <v>51</v>
+      </c>
+      <c r="AB81">
         <v>7</v>
       </c>
     </row>
@@ -4443,7 +4818,7 @@
         <v>3</v>
       </c>
       <c r="C82" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D82">
         <v>2</v>
@@ -4455,19 +4830,19 @@
         <v>-38</v>
       </c>
       <c r="G82" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H82" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I82" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="J82">
         <v>40</v>
       </c>
       <c r="K82" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L82">
         <v>6</v>
@@ -4478,19 +4853,25 @@
       <c r="O82">
         <v>9</v>
       </c>
-      <c r="R82" t="s">
-        <v>49</v>
-      </c>
-      <c r="S82" t="s">
-        <v>80</v>
-      </c>
-      <c r="U82" t="s">
-        <v>34</v>
-      </c>
-      <c r="W82">
-        <v>6</v>
-      </c>
-      <c r="X82">
+      <c r="P82" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>121</v>
+      </c>
+      <c r="S82">
+        <v>6</v>
+      </c>
+      <c r="W82" t="s">
+        <v>34</v>
+      </c>
+      <c r="X82" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z82" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB82">
         <v>7</v>
       </c>
     </row>
@@ -4502,7 +4883,7 @@
         <v>3</v>
       </c>
       <c r="C83" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D83">
         <v>1</v>
@@ -4514,36 +4895,45 @@
         <v>22</v>
       </c>
       <c r="G83" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H83" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I83" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J83">
         <v>12</v>
       </c>
       <c r="K83" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L83">
         <v>6</v>
       </c>
-      <c r="R83" t="s">
-        <v>30</v>
-      </c>
-      <c r="S83" t="s">
-        <v>56</v>
-      </c>
-      <c r="U83" t="s">
-        <v>30</v>
-      </c>
-      <c r="W83">
+      <c r="P83" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>71</v>
+      </c>
+      <c r="S83">
         <v>5</v>
       </c>
-      <c r="X83">
+      <c r="T83" t="s">
+        <v>122</v>
+      </c>
+      <c r="W83" t="s">
+        <v>34</v>
+      </c>
+      <c r="X83" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z83" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB83">
         <v>7</v>
       </c>
     </row>
@@ -4555,7 +4945,7 @@
         <v>3</v>
       </c>
       <c r="C84" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D84">
         <v>1</v>
@@ -4567,19 +4957,19 @@
         <v>10</v>
       </c>
       <c r="G84" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H84" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I84" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J84">
         <v>0</v>
       </c>
       <c r="K84" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L84">
         <v>8</v>
@@ -4590,16 +4980,28 @@
       <c r="O84">
         <v>3</v>
       </c>
-      <c r="R84" t="s">
-        <v>34</v>
+      <c r="P84" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>71</v>
       </c>
       <c r="S84" t="s">
-        <v>82</v>
-      </c>
-      <c r="U84" t="s">
-        <v>34</v>
-      </c>
-      <c r="X84">
+        <v>123</v>
+      </c>
+      <c r="T84" t="s">
+        <v>124</v>
+      </c>
+      <c r="W84" t="s">
+        <v>39</v>
+      </c>
+      <c r="X84" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z84" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB84">
         <v>7</v>
       </c>
     </row>
@@ -4611,7 +5013,7 @@
         <v>3</v>
       </c>
       <c r="C85" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D85">
         <v>2</v>
@@ -4623,19 +5025,19 @@
         <v>10</v>
       </c>
       <c r="G85" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H85" t="s">
+        <v>42</v>
+      </c>
+      <c r="I85" t="s">
+        <v>90</v>
+      </c>
+      <c r="J85">
+        <v>10</v>
+      </c>
+      <c r="K85" t="s">
         <v>37</v>
-      </c>
-      <c r="I85" t="s">
-        <v>76</v>
-      </c>
-      <c r="J85">
-        <v>10</v>
-      </c>
-      <c r="K85" t="s">
-        <v>33</v>
       </c>
       <c r="L85">
         <v>6</v>
@@ -4646,19 +5048,25 @@
       <c r="O85">
         <v>4</v>
       </c>
-      <c r="R85" t="s">
-        <v>34</v>
-      </c>
-      <c r="S85" t="s">
-        <v>101</v>
-      </c>
-      <c r="U85" t="s">
-        <v>30</v>
-      </c>
-      <c r="W85">
-        <v>6</v>
-      </c>
-      <c r="X85">
+      <c r="P85" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q85" t="s">
+        <v>88</v>
+      </c>
+      <c r="S85">
+        <v>6</v>
+      </c>
+      <c r="W85" t="s">
+        <v>39</v>
+      </c>
+      <c r="X85" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z85" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB85">
         <v>7</v>
       </c>
     </row>
@@ -4670,7 +5078,7 @@
         <v>3</v>
       </c>
       <c r="C86" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D86">
         <v>1</v>
@@ -4682,15 +5090,15 @@
         <v>3</v>
       </c>
       <c r="G86" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H86" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="I86" t="s">
-        <v>78</v>
-      </c>
-      <c r="X86">
+        <v>92</v>
+      </c>
+      <c r="AB86">
         <v>7</v>
       </c>
     </row>
@@ -4702,7 +5110,7 @@
         <v>3</v>
       </c>
       <c r="C87" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D87">
         <v>1</v>
@@ -4714,15 +5122,15 @@
         <v>-40</v>
       </c>
       <c r="G87" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H87" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I87" t="s">
-        <v>28</v>
-      </c>
-      <c r="X87">
+        <v>32</v>
+      </c>
+      <c r="AB87">
         <v>8</v>
       </c>
     </row>
@@ -4734,7 +5142,7 @@
         <v>3</v>
       </c>
       <c r="C88" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D88">
         <v>1</v>
@@ -4746,39 +5154,42 @@
         <v>-20</v>
       </c>
       <c r="G88" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H88" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I88" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J88">
         <v>4</v>
       </c>
       <c r="K88" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L88">
         <v>7</v>
       </c>
-      <c r="R88" t="s">
-        <v>30</v>
-      </c>
-      <c r="S88" t="s">
-        <v>74</v>
-      </c>
-      <c r="T88" t="s">
-        <v>102</v>
-      </c>
-      <c r="U88" t="s">
-        <v>34</v>
-      </c>
-      <c r="V88" t="s">
-        <v>34</v>
-      </c>
-      <c r="X88">
+      <c r="P88" t="s">
+        <v>47</v>
+      </c>
+      <c r="W88" t="s">
+        <v>34</v>
+      </c>
+      <c r="X88" t="s">
+        <v>87</v>
+      </c>
+      <c r="Y88" t="s">
+        <v>126</v>
+      </c>
+      <c r="Z88" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA88" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB88">
         <v>9</v>
       </c>
     </row>
@@ -4790,7 +5201,7 @@
         <v>3</v>
       </c>
       <c r="C89" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D89">
         <v>2</v>
@@ -4802,36 +5213,39 @@
         <v>-24</v>
       </c>
       <c r="G89" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H89" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I89" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J89">
         <v>7</v>
       </c>
       <c r="K89" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L89">
         <v>6</v>
       </c>
-      <c r="R89" t="s">
-        <v>34</v>
-      </c>
-      <c r="S89" t="s">
-        <v>39</v>
-      </c>
-      <c r="T89" t="s">
-        <v>103</v>
-      </c>
-      <c r="U89" t="s">
-        <v>34</v>
-      </c>
-      <c r="X89">
+      <c r="P89" t="s">
+        <v>52</v>
+      </c>
+      <c r="W89" t="s">
+        <v>39</v>
+      </c>
+      <c r="X89" t="s">
+        <v>44</v>
+      </c>
+      <c r="Y89" t="s">
+        <v>127</v>
+      </c>
+      <c r="Z89" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB89">
         <v>9</v>
       </c>
     </row>
@@ -4843,7 +5257,7 @@
         <v>3</v>
       </c>
       <c r="C90" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D90">
         <v>1</v>
@@ -4855,36 +5269,39 @@
         <v>-31</v>
       </c>
       <c r="G90" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H90" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I90" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J90">
         <v>2</v>
       </c>
       <c r="K90" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L90">
         <v>8</v>
       </c>
-      <c r="R90" t="s">
-        <v>49</v>
-      </c>
-      <c r="S90" t="s">
-        <v>50</v>
-      </c>
-      <c r="T90" t="s">
-        <v>79</v>
-      </c>
-      <c r="U90" t="s">
-        <v>34</v>
-      </c>
-      <c r="X90">
+      <c r="P90" t="s">
+        <v>47</v>
+      </c>
+      <c r="W90" t="s">
+        <v>56</v>
+      </c>
+      <c r="X90" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y90" t="s">
+        <v>93</v>
+      </c>
+      <c r="Z90" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB90">
         <v>9</v>
       </c>
     </row>
@@ -4896,7 +5313,7 @@
         <v>3</v>
       </c>
       <c r="C91" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D91">
         <v>2</v>
@@ -4908,36 +5325,39 @@
         <v>-33</v>
       </c>
       <c r="G91" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H91" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I91" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J91">
         <v>2</v>
       </c>
       <c r="K91" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L91">
         <v>6</v>
       </c>
-      <c r="R91" t="s">
-        <v>30</v>
-      </c>
-      <c r="S91" t="s">
-        <v>104</v>
-      </c>
-      <c r="T91" t="s">
-        <v>97</v>
-      </c>
-      <c r="U91" t="s">
-        <v>30</v>
-      </c>
-      <c r="X91">
+      <c r="P91" t="s">
+        <v>47</v>
+      </c>
+      <c r="W91" t="s">
+        <v>34</v>
+      </c>
+      <c r="X91" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y91" t="s">
+        <v>117</v>
+      </c>
+      <c r="Z91" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB91">
         <v>9</v>
       </c>
     </row>
@@ -4949,7 +5369,7 @@
         <v>3</v>
       </c>
       <c r="C92" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D92">
         <v>3</v>
@@ -4961,19 +5381,19 @@
         <v>-35</v>
       </c>
       <c r="G92" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H92" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I92" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="J92">
         <v>65</v>
       </c>
       <c r="K92" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L92">
         <v>5</v>
@@ -4984,19 +5404,22 @@
       <c r="O92">
         <v>8</v>
       </c>
-      <c r="R92" t="s">
-        <v>34</v>
-      </c>
-      <c r="S92" t="s">
-        <v>35</v>
-      </c>
-      <c r="T92" t="s">
-        <v>87</v>
-      </c>
-      <c r="U92" t="s">
-        <v>34</v>
-      </c>
-      <c r="X92">
+      <c r="P92" t="s">
+        <v>52</v>
+      </c>
+      <c r="W92" t="s">
+        <v>39</v>
+      </c>
+      <c r="X92" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y92" t="s">
+        <v>106</v>
+      </c>
+      <c r="Z92" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB92">
         <v>9</v>
       </c>
     </row>
@@ -5008,7 +5431,7 @@
         <v>3</v>
       </c>
       <c r="C93" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D93">
         <v>1</v>
@@ -5020,21 +5443,21 @@
         <v>3</v>
       </c>
       <c r="G93" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H93" t="s">
-        <v>105</v>
+        <v>129</v>
       </c>
       <c r="I93" t="s">
-        <v>78</v>
-      </c>
-      <c r="U93" t="s">
-        <v>34</v>
-      </c>
-      <c r="V93" t="s">
-        <v>34</v>
-      </c>
-      <c r="X93">
+        <v>92</v>
+      </c>
+      <c r="Z93" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA93" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB93">
         <v>9</v>
       </c>
     </row>
@@ -5046,7 +5469,7 @@
         <v>3</v>
       </c>
       <c r="C94" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D94">
         <v>1</v>
@@ -5058,15 +5481,15 @@
         <v>-40</v>
       </c>
       <c r="G94" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H94" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="I94" t="s">
-        <v>28</v>
-      </c>
-      <c r="X94">
+        <v>32</v>
+      </c>
+      <c r="AB94">
         <v>10</v>
       </c>
     </row>
@@ -5078,7 +5501,7 @@
         <v>3</v>
       </c>
       <c r="C95" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D95">
         <v>1</v>
@@ -5090,42 +5513,48 @@
         <v>-20</v>
       </c>
       <c r="G95" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H95" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I95" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J95">
         <v>-2</v>
       </c>
       <c r="K95" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L95">
         <v>6</v>
       </c>
       <c r="M95" t="s">
-        <v>73</v>
-      </c>
-      <c r="R95" t="s">
-        <v>30</v>
-      </c>
-      <c r="S95" t="s">
-        <v>47</v>
-      </c>
-      <c r="U95" t="s">
-        <v>34</v>
-      </c>
-      <c r="V95" t="s">
-        <v>30</v>
-      </c>
-      <c r="W95">
-        <v>3</v>
-      </c>
-      <c r="X95">
+        <v>85</v>
+      </c>
+      <c r="P95" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>71</v>
+      </c>
+      <c r="S95">
+        <v>3</v>
+      </c>
+      <c r="W95" t="s">
+        <v>34</v>
+      </c>
+      <c r="X95" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z95" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA95" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB95">
         <v>8</v>
       </c>
     </row>
@@ -5137,7 +5566,7 @@
         <v>3</v>
       </c>
       <c r="C96" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D96">
         <v>2</v>
@@ -5149,19 +5578,19 @@
         <v>-18</v>
       </c>
       <c r="G96" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H96" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I96" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J96">
         <v>0</v>
       </c>
       <c r="K96" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L96">
         <v>6</v>
@@ -5172,22 +5601,31 @@
       <c r="O96">
         <v>3</v>
       </c>
+      <c r="P96" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q96" t="s">
+        <v>71</v>
+      </c>
       <c r="R96" t="s">
-        <v>30</v>
-      </c>
-      <c r="S96" t="s">
-        <v>54</v>
-      </c>
-      <c r="U96" t="s">
-        <v>30</v>
-      </c>
-      <c r="V96" t="s">
-        <v>30</v>
-      </c>
-      <c r="W96">
-        <v>3</v>
-      </c>
-      <c r="X96">
+        <v>86</v>
+      </c>
+      <c r="S96">
+        <v>3</v>
+      </c>
+      <c r="W96" t="s">
+        <v>34</v>
+      </c>
+      <c r="X96" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z96" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA96" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB96">
         <v>8</v>
       </c>
     </row>
@@ -5199,7 +5637,7 @@
         <v>3</v>
       </c>
       <c r="C97" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D97">
         <v>3</v>
@@ -5211,19 +5649,19 @@
         <v>-18</v>
       </c>
       <c r="G97" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H97" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I97" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="J97">
         <v>17</v>
       </c>
       <c r="K97" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L97">
         <v>5</v>
@@ -5234,19 +5672,28 @@
       <c r="O97">
         <v>6</v>
       </c>
+      <c r="P97" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>71</v>
+      </c>
       <c r="R97" t="s">
-        <v>30</v>
-      </c>
-      <c r="S97" t="s">
-        <v>35</v>
-      </c>
-      <c r="U97" t="s">
-        <v>34</v>
-      </c>
-      <c r="W97">
-        <v>6</v>
-      </c>
-      <c r="X97">
+        <v>103</v>
+      </c>
+      <c r="S97">
+        <v>6</v>
+      </c>
+      <c r="W97" t="s">
+        <v>34</v>
+      </c>
+      <c r="X97" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z97" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB97">
         <v>8</v>
       </c>
     </row>
@@ -5258,7 +5705,7 @@
         <v>3</v>
       </c>
       <c r="C98" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -5270,19 +5717,19 @@
         <v>-35</v>
       </c>
       <c r="G98" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H98" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I98" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J98">
         <v>0</v>
       </c>
       <c r="K98" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L98">
         <v>6</v>
@@ -5293,19 +5740,28 @@
       <c r="O98">
         <v>3</v>
       </c>
-      <c r="R98" t="s">
-        <v>34</v>
+      <c r="P98" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q98" t="s">
+        <v>71</v>
       </c>
       <c r="S98" t="s">
-        <v>106</v>
-      </c>
-      <c r="U98" t="s">
-        <v>34</v>
-      </c>
-      <c r="W98">
-        <v>3</v>
-      </c>
-      <c r="X98">
+        <v>131</v>
+      </c>
+      <c r="T98" t="s">
+        <v>132</v>
+      </c>
+      <c r="W98" t="s">
+        <v>39</v>
+      </c>
+      <c r="X98" t="s">
+        <v>133</v>
+      </c>
+      <c r="Z98" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB98">
         <v>8</v>
       </c>
     </row>
@@ -5317,7 +5773,7 @@
         <v>3</v>
       </c>
       <c r="C99" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D99">
         <v>2</v>
@@ -5329,19 +5785,19 @@
         <v>-35</v>
       </c>
       <c r="G99" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H99" t="s">
+        <v>42</v>
+      </c>
+      <c r="I99" t="s">
+        <v>60</v>
+      </c>
+      <c r="J99">
+        <v>10</v>
+      </c>
+      <c r="K99" t="s">
         <v>37</v>
-      </c>
-      <c r="I99" t="s">
-        <v>53</v>
-      </c>
-      <c r="J99">
-        <v>10</v>
-      </c>
-      <c r="K99" t="s">
-        <v>33</v>
       </c>
       <c r="L99">
         <v>6</v>
@@ -5352,16 +5808,28 @@
       <c r="O99">
         <v>5</v>
       </c>
+      <c r="P99" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q99" t="s">
+        <v>71</v>
+      </c>
       <c r="R99" t="s">
-        <v>30</v>
-      </c>
-      <c r="S99" t="s">
-        <v>54</v>
-      </c>
-      <c r="U99" t="s">
-        <v>30</v>
-      </c>
-      <c r="X99">
+        <v>73</v>
+      </c>
+      <c r="S99">
+        <v>6</v>
+      </c>
+      <c r="W99" t="s">
+        <v>34</v>
+      </c>
+      <c r="X99" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z99" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB99">
         <v>8</v>
       </c>
     </row>
@@ -5373,7 +5841,7 @@
         <v>3</v>
       </c>
       <c r="C100" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D100">
         <v>1</v>
@@ -5385,42 +5853,48 @@
         <v>-45</v>
       </c>
       <c r="G100" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H100" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I100" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J100">
         <v>7</v>
       </c>
       <c r="K100" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L100">
         <v>6</v>
       </c>
       <c r="M100" t="s">
-        <v>93</v>
-      </c>
-      <c r="R100" t="s">
-        <v>34</v>
-      </c>
-      <c r="S100" t="s">
-        <v>54</v>
-      </c>
-      <c r="U100" t="s">
-        <v>30</v>
-      </c>
-      <c r="V100" t="s">
-        <v>30</v>
-      </c>
-      <c r="W100">
+        <v>113</v>
+      </c>
+      <c r="P100" t="s">
+        <v>52</v>
+      </c>
+      <c r="S100">
         <v>5</v>
       </c>
-      <c r="X100">
+      <c r="T100" t="s">
+        <v>122</v>
+      </c>
+      <c r="W100" t="s">
+        <v>39</v>
+      </c>
+      <c r="X100" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z100" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA100" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB100">
         <v>8</v>
       </c>
     </row>
@@ -5432,7 +5906,7 @@
         <v>3</v>
       </c>
       <c r="C101" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D101">
         <v>2</v>
@@ -5444,27 +5918,33 @@
         <v>48</v>
       </c>
       <c r="G101" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I101" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="J101">
         <v>5</v>
       </c>
       <c r="K101" t="s">
-        <v>33</v>
-      </c>
-      <c r="R101" t="s">
-        <v>34</v>
-      </c>
-      <c r="S101" t="s">
-        <v>47</v>
-      </c>
-      <c r="V101" t="s">
-        <v>34</v>
-      </c>
-      <c r="X101">
+        <v>37</v>
+      </c>
+      <c r="P101" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q101" t="s">
+        <v>73</v>
+      </c>
+      <c r="W101" t="s">
+        <v>39</v>
+      </c>
+      <c r="X101" t="s">
+        <v>54</v>
+      </c>
+      <c r="AA101" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB101">
         <v>8</v>
       </c>
     </row>
@@ -5476,7 +5956,7 @@
         <v>3</v>
       </c>
       <c r="C102" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D102">
         <v>1</v>
@@ -5488,19 +5968,19 @@
         <v>43</v>
       </c>
       <c r="G102" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H102" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I102" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J102">
         <v>0</v>
       </c>
       <c r="K102" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L102">
         <v>8</v>
@@ -5511,16 +5991,28 @@
       <c r="O102">
         <v>4</v>
       </c>
-      <c r="R102" t="s">
-        <v>34</v>
+      <c r="P102" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q102" t="s">
+        <v>71</v>
       </c>
       <c r="S102" t="s">
-        <v>82</v>
-      </c>
-      <c r="U102" t="s">
-        <v>30</v>
-      </c>
-      <c r="X102">
+        <v>131</v>
+      </c>
+      <c r="T102" t="s">
+        <v>134</v>
+      </c>
+      <c r="W102" t="s">
+        <v>39</v>
+      </c>
+      <c r="X102" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z102" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB102">
         <v>8</v>
       </c>
     </row>
@@ -5532,7 +6024,7 @@
         <v>3</v>
       </c>
       <c r="C103" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D103">
         <v>2</v>
@@ -5544,42 +6036,48 @@
         <v>43</v>
       </c>
       <c r="G103" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H103" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I103" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J103">
         <v>2</v>
       </c>
       <c r="K103" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L103">
         <v>6</v>
       </c>
       <c r="M103" t="s">
-        <v>62</v>
-      </c>
-      <c r="R103" t="s">
-        <v>34</v>
+        <v>72</v>
+      </c>
+      <c r="P103" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q103" t="s">
+        <v>135</v>
       </c>
       <c r="S103" t="s">
-        <v>54</v>
-      </c>
-      <c r="U103" t="s">
-        <v>34</v>
-      </c>
-      <c r="V103" t="s">
-        <v>30</v>
+        <v>131</v>
       </c>
       <c r="W103" t="s">
-        <v>107</v>
-      </c>
-      <c r="X103">
+        <v>39</v>
+      </c>
+      <c r="X103" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z103" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA103" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB103">
         <v>8</v>
       </c>
     </row>
@@ -5591,7 +6089,7 @@
         <v>3</v>
       </c>
       <c r="C104" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D104">
         <v>3</v>
@@ -5603,36 +6101,45 @@
         <v>41</v>
       </c>
       <c r="G104" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H104" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I104" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="J104">
         <v>-4</v>
       </c>
       <c r="K104" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L104">
         <v>6</v>
       </c>
+      <c r="P104" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q104" t="s">
+        <v>71</v>
+      </c>
       <c r="R104" t="s">
-        <v>49</v>
-      </c>
-      <c r="S104" t="s">
-        <v>80</v>
-      </c>
-      <c r="U104" t="s">
-        <v>30</v>
-      </c>
-      <c r="W104">
-        <v>6</v>
-      </c>
-      <c r="X104">
+        <v>136</v>
+      </c>
+      <c r="S104">
+        <v>6</v>
+      </c>
+      <c r="W104" t="s">
+        <v>39</v>
+      </c>
+      <c r="X104" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z104" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB104">
         <v>8</v>
       </c>
     </row>
@@ -5644,7 +6151,7 @@
         <v>3</v>
       </c>
       <c r="C105" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D105">
         <v>4</v>
@@ -5656,15 +6163,15 @@
         <v>45</v>
       </c>
       <c r="G105" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H105" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="I105" t="s">
-        <v>88</v>
-      </c>
-      <c r="X105">
+        <v>107</v>
+      </c>
+      <c r="AB105">
         <v>8</v>
       </c>
     </row>
@@ -5676,7 +6183,7 @@
         <v>3</v>
       </c>
       <c r="C106" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D106">
         <v>1</v>
@@ -5688,36 +6195,39 @@
         <v>-3</v>
       </c>
       <c r="G106" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H106" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I106" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J106">
         <v>0</v>
       </c>
       <c r="K106" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L106">
         <v>7</v>
       </c>
-      <c r="Q106">
+      <c r="P106" t="s">
+        <v>47</v>
+      </c>
+      <c r="V106">
         <v>0</v>
       </c>
-      <c r="R106" t="s">
-        <v>30</v>
-      </c>
-      <c r="S106" t="s">
-        <v>82</v>
-      </c>
-      <c r="U106" t="s">
-        <v>30</v>
-      </c>
-      <c r="X106">
+      <c r="W106" t="s">
+        <v>34</v>
+      </c>
+      <c r="X106" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z106" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB106">
         <v>10</v>
       </c>
     </row>
@@ -5729,7 +6239,7 @@
         <v>3</v>
       </c>
       <c r="C107" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D107">
         <v>2</v>
@@ -5741,33 +6251,36 @@
         <v>-3</v>
       </c>
       <c r="G107" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H107" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I107" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J107">
         <v>5</v>
       </c>
       <c r="K107" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L107">
         <v>6</v>
       </c>
-      <c r="R107" t="s">
-        <v>30</v>
-      </c>
-      <c r="S107" t="s">
-        <v>39</v>
-      </c>
-      <c r="U107" t="s">
-        <v>34</v>
-      </c>
-      <c r="X107">
+      <c r="P107" t="s">
+        <v>38</v>
+      </c>
+      <c r="W107" t="s">
+        <v>34</v>
+      </c>
+      <c r="X107" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z107" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB107">
         <v>10</v>
       </c>
     </row>
@@ -5779,7 +6292,7 @@
         <v>3</v>
       </c>
       <c r="C108" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D108">
         <v>3</v>
@@ -5791,19 +6304,19 @@
         <v>-8</v>
       </c>
       <c r="G108" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H108" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I108" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="J108">
         <v>13</v>
       </c>
       <c r="K108" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L108">
         <v>6</v>
@@ -5814,19 +6327,22 @@
       <c r="O108">
         <v>6</v>
       </c>
-      <c r="R108" t="s">
-        <v>30</v>
-      </c>
-      <c r="S108" t="s">
-        <v>54</v>
-      </c>
-      <c r="U108" t="s">
-        <v>34</v>
-      </c>
-      <c r="V108" t="s">
-        <v>34</v>
-      </c>
-      <c r="X108">
+      <c r="P108" t="s">
+        <v>38</v>
+      </c>
+      <c r="W108" t="s">
+        <v>34</v>
+      </c>
+      <c r="X108" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z108" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA108" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB108">
         <v>10</v>
       </c>
     </row>
@@ -5838,7 +6354,7 @@
         <v>3</v>
       </c>
       <c r="C109" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D109">
         <v>1</v>
@@ -5850,33 +6366,36 @@
         <v>-21</v>
       </c>
       <c r="G109" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H109" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I109" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J109">
         <v>13</v>
       </c>
       <c r="K109" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L109">
         <v>6</v>
       </c>
-      <c r="R109" t="s">
-        <v>30</v>
-      </c>
-      <c r="S109" t="s">
-        <v>39</v>
-      </c>
-      <c r="U109" t="s">
-        <v>30</v>
-      </c>
-      <c r="X109">
+      <c r="P109" t="s">
+        <v>38</v>
+      </c>
+      <c r="W109" t="s">
+        <v>34</v>
+      </c>
+      <c r="X109" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z109" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB109">
         <v>10</v>
       </c>
     </row>
@@ -5888,7 +6407,7 @@
         <v>3</v>
       </c>
       <c r="C110" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D110">
         <v>1</v>
@@ -5900,33 +6419,36 @@
         <v>-34</v>
       </c>
       <c r="G110" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H110" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I110" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J110">
         <v>3</v>
       </c>
       <c r="K110" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L110">
         <v>7</v>
       </c>
-      <c r="R110" t="s">
-        <v>49</v>
-      </c>
-      <c r="S110" t="s">
-        <v>50</v>
-      </c>
-      <c r="U110" t="s">
-        <v>34</v>
-      </c>
-      <c r="X110">
+      <c r="P110" t="s">
+        <v>47</v>
+      </c>
+      <c r="W110" t="s">
+        <v>56</v>
+      </c>
+      <c r="X110" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z110" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB110">
         <v>10</v>
       </c>
     </row>
@@ -5938,7 +6460,7 @@
         <v>3</v>
       </c>
       <c r="C111" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D111">
         <v>2</v>
@@ -5950,33 +6472,36 @@
         <v>-37</v>
       </c>
       <c r="G111" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H111" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I111" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J111">
         <v>34</v>
       </c>
       <c r="K111" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L111">
         <v>6</v>
       </c>
-      <c r="R111" t="s">
-        <v>30</v>
-      </c>
-      <c r="S111" t="s">
-        <v>39</v>
-      </c>
-      <c r="U111" t="s">
-        <v>34</v>
-      </c>
-      <c r="X111">
+      <c r="P111" t="s">
+        <v>52</v>
+      </c>
+      <c r="W111" t="s">
+        <v>34</v>
+      </c>
+      <c r="X111" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z111" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB111">
         <v>10</v>
       </c>
     </row>
@@ -5988,7 +6513,7 @@
         <v>3</v>
       </c>
       <c r="C112" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D112">
         <v>1</v>
@@ -6000,18 +6525,18 @@
         <v>29</v>
       </c>
       <c r="G112" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="I112" t="s">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="J112">
         <v>0</v>
       </c>
       <c r="K112" t="s">
-        <v>33</v>
-      </c>
-      <c r="X112">
+        <v>37</v>
+      </c>
+      <c r="AB112">
         <v>10</v>
       </c>
     </row>
@@ -6023,7 +6548,7 @@
         <v>3</v>
       </c>
       <c r="C113" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D113">
         <v>1</v>
@@ -6035,33 +6560,36 @@
         <v>29</v>
       </c>
       <c r="G113" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H113" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I113" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J113">
         <v>2</v>
       </c>
       <c r="K113" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L113">
         <v>6</v>
       </c>
-      <c r="R113" t="s">
-        <v>30</v>
-      </c>
-      <c r="S113" t="s">
-        <v>39</v>
-      </c>
-      <c r="U113" t="s">
-        <v>34</v>
-      </c>
-      <c r="X113">
+      <c r="P113" t="s">
+        <v>52</v>
+      </c>
+      <c r="W113" t="s">
+        <v>34</v>
+      </c>
+      <c r="X113" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z113" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB113">
         <v>10</v>
       </c>
     </row>
@@ -6073,7 +6601,7 @@
         <v>4</v>
       </c>
       <c r="C114" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D114">
         <v>2</v>
@@ -6085,33 +6613,36 @@
         <v>27</v>
       </c>
       <c r="G114" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H114" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I114" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J114">
         <v>0</v>
       </c>
       <c r="K114" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L114">
         <v>7</v>
       </c>
-      <c r="R114" t="s">
-        <v>49</v>
-      </c>
-      <c r="S114" t="s">
-        <v>50</v>
-      </c>
-      <c r="U114" t="s">
-        <v>30</v>
-      </c>
-      <c r="X114">
+      <c r="P114" t="s">
+        <v>47</v>
+      </c>
+      <c r="W114" t="s">
+        <v>56</v>
+      </c>
+      <c r="X114" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z114" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB114">
         <v>10</v>
       </c>
     </row>
@@ -6123,7 +6654,7 @@
         <v>4</v>
       </c>
       <c r="C115" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D115">
         <v>3</v>
@@ -6135,33 +6666,36 @@
         <v>27</v>
       </c>
       <c r="G115" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H115" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I115" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="J115">
         <v>-9</v>
       </c>
       <c r="K115" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L115">
         <v>6</v>
       </c>
-      <c r="R115" t="s">
-        <v>30</v>
-      </c>
-      <c r="S115" t="s">
-        <v>39</v>
-      </c>
-      <c r="U115" t="s">
-        <v>30</v>
-      </c>
-      <c r="X115">
+      <c r="P115" t="s">
+        <v>38</v>
+      </c>
+      <c r="W115" t="s">
+        <v>34</v>
+      </c>
+      <c r="X115" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z115" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB115">
         <v>10</v>
       </c>
     </row>
@@ -6173,7 +6707,7 @@
         <v>4</v>
       </c>
       <c r="C116" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D116">
         <v>4</v>
@@ -6185,15 +6719,15 @@
         <v>36</v>
       </c>
       <c r="G116" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H116" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="I116" t="s">
-        <v>28</v>
-      </c>
-      <c r="X116">
+        <v>32</v>
+      </c>
+      <c r="AB116">
         <v>10</v>
       </c>
     </row>
@@ -6205,7 +6739,7 @@
         <v>4</v>
       </c>
       <c r="C117" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D117">
         <v>1</v>
@@ -6217,42 +6751,48 @@
         <v>-20</v>
       </c>
       <c r="G117" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H117" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I117" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J117">
         <v>6</v>
       </c>
       <c r="K117" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L117">
         <v>6</v>
       </c>
       <c r="M117" t="s">
-        <v>61</v>
-      </c>
-      <c r="R117" t="s">
-        <v>34</v>
-      </c>
-      <c r="S117" t="s">
-        <v>35</v>
-      </c>
-      <c r="U117" t="s">
-        <v>34</v>
-      </c>
-      <c r="V117" t="s">
-        <v>34</v>
-      </c>
-      <c r="W117">
-        <v>3</v>
-      </c>
-      <c r="X117">
+        <v>69</v>
+      </c>
+      <c r="P117" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q117" t="s">
+        <v>71</v>
+      </c>
+      <c r="S117">
+        <v>3</v>
+      </c>
+      <c r="W117" t="s">
+        <v>39</v>
+      </c>
+      <c r="X117" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z117" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA117" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB117">
         <v>9</v>
       </c>
     </row>
@@ -6264,7 +6804,7 @@
         <v>4</v>
       </c>
       <c r="C118" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D118">
         <v>2</v>
@@ -6276,19 +6816,19 @@
         <v>-26</v>
       </c>
       <c r="G118" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H118" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I118" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J118">
         <v>0</v>
       </c>
       <c r="K118" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L118">
         <v>6</v>
@@ -6299,19 +6839,28 @@
       <c r="O118">
         <v>5</v>
       </c>
+      <c r="P118" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q118" t="s">
+        <v>71</v>
+      </c>
       <c r="R118" t="s">
-        <v>34</v>
-      </c>
-      <c r="S118" t="s">
-        <v>39</v>
-      </c>
-      <c r="U118" t="s">
-        <v>34</v>
+        <v>73</v>
+      </c>
+      <c r="S118">
+        <v>3</v>
       </c>
       <c r="W118" t="s">
-        <v>108</v>
-      </c>
-      <c r="X118">
+        <v>39</v>
+      </c>
+      <c r="X118" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z118" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB118">
         <v>9</v>
       </c>
     </row>
@@ -6323,7 +6872,7 @@
         <v>4</v>
       </c>
       <c r="C119" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D119">
         <v>3</v>
@@ -6335,39 +6884,48 @@
         <v>-26</v>
       </c>
       <c r="G119" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H119" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I119" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="J119">
         <v>-11</v>
       </c>
       <c r="K119" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L119">
         <v>6</v>
       </c>
+      <c r="P119" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q119" t="s">
+        <v>71</v>
+      </c>
       <c r="R119" t="s">
-        <v>34</v>
-      </c>
-      <c r="S119" t="s">
-        <v>54</v>
-      </c>
-      <c r="U119" t="s">
-        <v>34</v>
-      </c>
-      <c r="V119" t="s">
-        <v>34</v>
-      </c>
-      <c r="W119">
-        <v>3</v>
-      </c>
-      <c r="X119">
+        <v>136</v>
+      </c>
+      <c r="S119">
+        <v>3</v>
+      </c>
+      <c r="W119" t="s">
+        <v>39</v>
+      </c>
+      <c r="X119" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z119" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA119" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB119">
         <v>9</v>
       </c>
     </row>
@@ -6379,7 +6937,7 @@
         <v>4</v>
       </c>
       <c r="C120" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D120">
         <v>4</v>
@@ -6391,18 +6949,18 @@
         <v>-15</v>
       </c>
       <c r="G120" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H120" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="I120" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q120">
+        <v>76</v>
+      </c>
+      <c r="V120">
         <v>11</v>
       </c>
-      <c r="X120">
+      <c r="AB120">
         <v>9</v>
       </c>
     </row>
@@ -6414,7 +6972,7 @@
         <v>4</v>
       </c>
       <c r="C121" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D121">
         <v>1</v>
@@ -6426,33 +6984,36 @@
         <v>41</v>
       </c>
       <c r="G121" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H121" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I121" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J121">
         <v>1</v>
       </c>
       <c r="K121" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L121">
         <v>7</v>
       </c>
-      <c r="R121" t="s">
-        <v>49</v>
-      </c>
-      <c r="S121" t="s">
-        <v>50</v>
-      </c>
-      <c r="U121" t="s">
-        <v>34</v>
-      </c>
-      <c r="X121">
+      <c r="P121" t="s">
+        <v>47</v>
+      </c>
+      <c r="W121" t="s">
+        <v>56</v>
+      </c>
+      <c r="X121" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z121" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB121">
         <v>11</v>
       </c>
     </row>
@@ -6464,7 +7025,7 @@
         <v>4</v>
       </c>
       <c r="C122" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D122">
         <v>2</v>
@@ -6476,19 +7037,19 @@
         <v>40</v>
       </c>
       <c r="G122" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H122" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I122" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J122">
         <v>0</v>
       </c>
       <c r="K122" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L122">
         <v>7</v>
@@ -6499,16 +7060,19 @@
       <c r="O122">
         <v>1</v>
       </c>
-      <c r="R122" t="s">
-        <v>30</v>
-      </c>
-      <c r="S122" t="s">
-        <v>82</v>
-      </c>
-      <c r="U122" t="s">
-        <v>30</v>
-      </c>
-      <c r="X122">
+      <c r="P122" t="s">
+        <v>47</v>
+      </c>
+      <c r="W122" t="s">
+        <v>34</v>
+      </c>
+      <c r="X122" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z122" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB122">
         <v>11</v>
       </c>
     </row>
@@ -6520,7 +7084,7 @@
         <v>4</v>
       </c>
       <c r="C123" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D123">
         <v>3</v>
@@ -6532,19 +7096,19 @@
         <v>40</v>
       </c>
       <c r="G123" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H123" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I123" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="J123">
         <v>40</v>
       </c>
       <c r="K123" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L123">
         <v>5</v>
@@ -6555,19 +7119,22 @@
       <c r="O123">
         <v>9</v>
       </c>
-      <c r="R123" t="s">
-        <v>49</v>
-      </c>
-      <c r="S123" t="s">
-        <v>80</v>
-      </c>
-      <c r="U123" t="s">
-        <v>34</v>
-      </c>
-      <c r="V123" t="s">
-        <v>30</v>
-      </c>
-      <c r="X123">
+      <c r="P123" t="s">
+        <v>47</v>
+      </c>
+      <c r="W123" t="s">
+        <v>56</v>
+      </c>
+      <c r="X123" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z123" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA123" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB123">
         <v>11</v>
       </c>
     </row>
@@ -6579,7 +7146,7 @@
         <v>4</v>
       </c>
       <c r="C124" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D124">
         <v>1</v>
@@ -6591,15 +7158,15 @@
         <v>3</v>
       </c>
       <c r="G124" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H124" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
       <c r="I124" t="s">
-        <v>78</v>
-      </c>
-      <c r="X124">
+        <v>92</v>
+      </c>
+      <c r="AB124">
         <v>11</v>
       </c>
     </row>
@@ -6611,7 +7178,7 @@
         <v>4</v>
       </c>
       <c r="C125" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D125">
         <v>1</v>
@@ -6623,18 +7190,18 @@
         <v>-40</v>
       </c>
       <c r="G125" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H125" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="I125" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q125">
+        <v>76</v>
+      </c>
+      <c r="V125">
         <v>17</v>
       </c>
-      <c r="X125">
+      <c r="AB125">
         <v>12</v>
       </c>
     </row>
@@ -6646,7 +7213,7 @@
         <v>4</v>
       </c>
       <c r="C126" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D126">
         <v>1</v>
@@ -6658,39 +7225,45 @@
         <v>-22</v>
       </c>
       <c r="G126" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H126" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I126" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J126">
         <v>-4</v>
       </c>
       <c r="K126" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L126">
         <v>5</v>
       </c>
       <c r="M126" t="s">
-        <v>61</v>
-      </c>
-      <c r="R126" t="s">
-        <v>34</v>
-      </c>
-      <c r="S126" t="s">
-        <v>35</v>
-      </c>
-      <c r="U126" t="s">
-        <v>34</v>
-      </c>
-      <c r="W126">
-        <v>6</v>
-      </c>
-      <c r="X126">
+        <v>69</v>
+      </c>
+      <c r="P126" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q126" t="s">
+        <v>86</v>
+      </c>
+      <c r="S126">
+        <v>6</v>
+      </c>
+      <c r="W126" t="s">
+        <v>39</v>
+      </c>
+      <c r="X126" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z126" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB126">
         <v>10</v>
       </c>
     </row>
@@ -6702,7 +7275,7 @@
         <v>4</v>
       </c>
       <c r="C127" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D127">
         <v>2</v>
@@ -6714,19 +7287,19 @@
         <v>-18</v>
       </c>
       <c r="G127" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H127" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I127" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J127">
         <v>0</v>
       </c>
       <c r="K127" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L127">
         <v>5</v>
@@ -6737,16 +7310,25 @@
       <c r="O127">
         <v>5</v>
       </c>
+      <c r="P127" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q127" t="s">
+        <v>71</v>
+      </c>
       <c r="R127" t="s">
-        <v>34</v>
-      </c>
-      <c r="U127" t="s">
-        <v>30</v>
-      </c>
-      <c r="W127">
-        <v>6</v>
-      </c>
-      <c r="X127">
+        <v>103</v>
+      </c>
+      <c r="S127">
+        <v>6</v>
+      </c>
+      <c r="W127" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z127" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB127">
         <v>10</v>
       </c>
     </row>
@@ -6758,7 +7340,7 @@
         <v>4</v>
       </c>
       <c r="C128" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D128">
         <v>3</v>
@@ -6770,19 +7352,19 @@
         <v>-18</v>
       </c>
       <c r="G128" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H128" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I128" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J128">
         <v>0</v>
       </c>
       <c r="K128" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L128">
         <v>6</v>
@@ -6793,19 +7375,28 @@
       <c r="O128">
         <v>4</v>
       </c>
+      <c r="P128" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q128" t="s">
+        <v>71</v>
+      </c>
       <c r="R128" t="s">
-        <v>34</v>
-      </c>
-      <c r="S128" t="s">
-        <v>54</v>
-      </c>
-      <c r="U128" t="s">
-        <v>34</v>
-      </c>
-      <c r="W128">
-        <v>6</v>
-      </c>
-      <c r="X128">
+        <v>103</v>
+      </c>
+      <c r="S128">
+        <v>6</v>
+      </c>
+      <c r="W128" t="s">
+        <v>39</v>
+      </c>
+      <c r="X128" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z128" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB128">
         <v>10</v>
       </c>
     </row>
@@ -6817,7 +7408,7 @@
         <v>4</v>
       </c>
       <c r="C129" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D129">
         <v>4</v>
@@ -6829,15 +7420,15 @@
         <v>-18</v>
       </c>
       <c r="G129" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H129" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="I129" t="s">
-        <v>95</v>
-      </c>
-      <c r="X129">
+        <v>115</v>
+      </c>
+      <c r="AB129">
         <v>10</v>
       </c>
     </row>
@@ -6849,7 +7440,7 @@
         <v>4</v>
       </c>
       <c r="C130" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D130">
         <v>1</v>
@@ -6861,36 +7452,39 @@
         <v>-49</v>
       </c>
       <c r="G130" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H130" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I130" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J130">
         <v>47</v>
       </c>
       <c r="K130" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L130">
         <v>7</v>
       </c>
-      <c r="R130" t="s">
-        <v>34</v>
-      </c>
-      <c r="S130" t="s">
-        <v>74</v>
-      </c>
-      <c r="U130" t="s">
-        <v>34</v>
-      </c>
-      <c r="V130" t="s">
-        <v>30</v>
-      </c>
-      <c r="X130">
+      <c r="P130" t="s">
+        <v>47</v>
+      </c>
+      <c r="W130" t="s">
+        <v>39</v>
+      </c>
+      <c r="X130" t="s">
+        <v>87</v>
+      </c>
+      <c r="Z130" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA130" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB130">
         <v>12</v>
       </c>
     </row>
@@ -6902,7 +7496,7 @@
         <v>4</v>
       </c>
       <c r="C131" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D131">
         <v>1</v>
@@ -6914,30 +7508,33 @@
         <v>4</v>
       </c>
       <c r="G131" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H131" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I131" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="J131">
         <v>-5</v>
       </c>
       <c r="K131" t="s">
-        <v>33</v>
-      </c>
-      <c r="R131" t="s">
-        <v>49</v>
-      </c>
-      <c r="S131" t="s">
-        <v>50</v>
-      </c>
-      <c r="U131" t="s">
-        <v>30</v>
-      </c>
-      <c r="X131">
+        <v>37</v>
+      </c>
+      <c r="P131" t="s">
+        <v>47</v>
+      </c>
+      <c r="W131" t="s">
+        <v>56</v>
+      </c>
+      <c r="X131" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z131" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB131">
         <v>12</v>
       </c>
     </row>
@@ -6949,7 +7546,7 @@
         <v>4</v>
       </c>
       <c r="C132" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D132">
         <v>1</v>
@@ -6961,33 +7558,36 @@
         <v>9</v>
       </c>
       <c r="G132" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H132" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I132" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J132">
         <v>4</v>
       </c>
       <c r="K132" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L132">
         <v>7</v>
       </c>
-      <c r="R132" t="s">
-        <v>30</v>
-      </c>
-      <c r="S132" t="s">
-        <v>106</v>
-      </c>
-      <c r="U132" t="s">
-        <v>34</v>
-      </c>
-      <c r="X132">
+      <c r="P132" t="s">
+        <v>137</v>
+      </c>
+      <c r="W132" t="s">
+        <v>34</v>
+      </c>
+      <c r="X132" t="s">
+        <v>133</v>
+      </c>
+      <c r="Z132" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB132">
         <v>12</v>
       </c>
     </row>
@@ -6999,7 +7599,7 @@
         <v>4</v>
       </c>
       <c r="C133" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D133">
         <v>2</v>
@@ -7011,36 +7611,39 @@
         <v>5</v>
       </c>
       <c r="G133" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H133" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I133" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J133">
         <v>1</v>
       </c>
       <c r="K133" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L133">
         <v>8</v>
       </c>
-      <c r="R133" t="s">
-        <v>34</v>
-      </c>
-      <c r="S133" t="s">
-        <v>91</v>
-      </c>
-      <c r="U133" t="s">
-        <v>34</v>
-      </c>
-      <c r="V133" t="s">
-        <v>30</v>
-      </c>
-      <c r="X133">
+      <c r="P133" t="s">
+        <v>110</v>
+      </c>
+      <c r="W133" t="s">
+        <v>39</v>
+      </c>
+      <c r="X133" t="s">
+        <v>111</v>
+      </c>
+      <c r="Z133" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA133" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB133">
         <v>12</v>
       </c>
     </row>
@@ -7052,7 +7655,7 @@
         <v>4</v>
       </c>
       <c r="C134" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D134">
         <v>3</v>
@@ -7064,33 +7667,33 @@
         <v>4</v>
       </c>
       <c r="G134" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H134" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I134" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J134">
         <v>-3</v>
       </c>
       <c r="K134" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L134">
         <v>10</v>
       </c>
-      <c r="R134" t="s">
-        <v>30</v>
-      </c>
-      <c r="S134" t="s">
-        <v>74</v>
-      </c>
-      <c r="U134" t="s">
-        <v>30</v>
-      </c>
-      <c r="X134">
+      <c r="W134" t="s">
+        <v>34</v>
+      </c>
+      <c r="X134" t="s">
+        <v>87</v>
+      </c>
+      <c r="Z134" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB134">
         <v>12</v>
       </c>
     </row>
@@ -7102,7 +7705,7 @@
         <v>4</v>
       </c>
       <c r="C135" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D135">
         <v>4</v>
@@ -7114,15 +7717,15 @@
         <v>7</v>
       </c>
       <c r="G135" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H135" t="s">
-        <v>99</v>
+        <v>119</v>
       </c>
       <c r="I135" t="s">
-        <v>78</v>
-      </c>
-      <c r="X135">
+        <v>92</v>
+      </c>
+      <c r="AB135">
         <v>12</v>
       </c>
     </row>
@@ -7134,7 +7737,7 @@
         <v>4</v>
       </c>
       <c r="C136" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D136">
         <v>1</v>
@@ -7146,15 +7749,15 @@
         <v>-40</v>
       </c>
       <c r="G136" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H136" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="I136" t="s">
-        <v>28</v>
-      </c>
-      <c r="X136">
+        <v>32</v>
+      </c>
+      <c r="AB136">
         <v>12</v>
       </c>
     </row>
@@ -7166,7 +7769,7 @@
         <v>4</v>
       </c>
       <c r="C137" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D137">
         <v>1</v>
@@ -7178,19 +7781,19 @@
         <v>-20</v>
       </c>
       <c r="G137" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H137" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I137" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="J137">
         <v>80</v>
       </c>
       <c r="K137" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L137">
         <v>6</v>
@@ -7201,19 +7804,25 @@
       <c r="O137">
         <v>1</v>
       </c>
-      <c r="R137" t="s">
-        <v>34</v>
-      </c>
-      <c r="S137" t="s">
-        <v>54</v>
-      </c>
-      <c r="U137" t="s">
-        <v>30</v>
-      </c>
-      <c r="W137">
-        <v>6</v>
-      </c>
-      <c r="X137">
+      <c r="P137" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q137" t="s">
+        <v>71</v>
+      </c>
+      <c r="S137">
+        <v>6</v>
+      </c>
+      <c r="W137" t="s">
+        <v>39</v>
+      </c>
+      <c r="X137" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z137" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB137">
         <v>11</v>
       </c>
     </row>
@@ -7225,7 +7834,7 @@
         <v>4</v>
       </c>
       <c r="C138" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D138">
         <v>1</v>
@@ -7237,15 +7846,15 @@
         <v>3</v>
       </c>
       <c r="G138" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H138" t="s">
-        <v>77</v>
+        <v>91</v>
       </c>
       <c r="I138" t="s">
-        <v>78</v>
-      </c>
-      <c r="X138">
+        <v>92</v>
+      </c>
+      <c r="AB138">
         <v>11</v>
       </c>
     </row>
@@ -7257,7 +7866,7 @@
         <v>4</v>
       </c>
       <c r="C139" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D139">
         <v>1</v>
@@ -7269,15 +7878,15 @@
         <v>-40</v>
       </c>
       <c r="G139" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H139" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I139" t="s">
-        <v>28</v>
-      </c>
-      <c r="X139">
+        <v>32</v>
+      </c>
+      <c r="AB139">
         <v>12</v>
       </c>
     </row>
@@ -7289,7 +7898,7 @@
         <v>4</v>
       </c>
       <c r="C140" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D140">
         <v>1</v>
@@ -7301,36 +7910,39 @@
         <v>-20</v>
       </c>
       <c r="G140" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H140" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I140" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J140">
         <v>1</v>
       </c>
       <c r="K140" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L140">
         <v>7</v>
       </c>
-      <c r="R140" t="s">
-        <v>34</v>
-      </c>
-      <c r="S140" t="s">
-        <v>74</v>
-      </c>
-      <c r="U140" t="s">
-        <v>34</v>
-      </c>
-      <c r="V140" t="s">
-        <v>30</v>
-      </c>
-      <c r="X140">
+      <c r="P140" t="s">
+        <v>70</v>
+      </c>
+      <c r="W140" t="s">
+        <v>39</v>
+      </c>
+      <c r="X140" t="s">
+        <v>87</v>
+      </c>
+      <c r="Z140" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA140" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB140">
         <v>13</v>
       </c>
     </row>
@@ -7342,7 +7954,7 @@
         <v>4</v>
       </c>
       <c r="C141" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D141">
         <v>2</v>
@@ -7354,33 +7966,36 @@
         <v>-21</v>
       </c>
       <c r="G141" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H141" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I141" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J141">
         <v>57</v>
       </c>
       <c r="K141" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L141">
         <v>8</v>
       </c>
-      <c r="R141" t="s">
-        <v>49</v>
-      </c>
-      <c r="S141" t="s">
-        <v>50</v>
-      </c>
-      <c r="U141" t="s">
-        <v>30</v>
-      </c>
-      <c r="X141">
+      <c r="P141" t="s">
+        <v>47</v>
+      </c>
+      <c r="W141" t="s">
+        <v>56</v>
+      </c>
+      <c r="X141" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z141" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB141">
         <v>13</v>
       </c>
     </row>
@@ -7392,7 +8007,7 @@
         <v>4</v>
       </c>
       <c r="C142" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D142">
         <v>1</v>
@@ -7404,33 +8019,36 @@
         <v>22</v>
       </c>
       <c r="G142" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H142" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I142" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J142">
         <v>2</v>
       </c>
       <c r="K142" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L142">
         <v>7</v>
       </c>
-      <c r="R142" t="s">
-        <v>34</v>
-      </c>
-      <c r="S142" t="s">
-        <v>82</v>
-      </c>
-      <c r="U142" t="s">
-        <v>30</v>
-      </c>
-      <c r="X142">
+      <c r="P142" t="s">
+        <v>47</v>
+      </c>
+      <c r="W142" t="s">
+        <v>39</v>
+      </c>
+      <c r="X142" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z142" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB142">
         <v>13</v>
       </c>
     </row>
@@ -7442,7 +8060,7 @@
         <v>4</v>
       </c>
       <c r="C143" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D143">
         <v>2</v>
@@ -7454,36 +8072,39 @@
         <v>20</v>
       </c>
       <c r="G143" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H143" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I143" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J143">
         <v>-1</v>
       </c>
       <c r="K143" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L143">
         <v>6</v>
       </c>
-      <c r="R143" t="s">
-        <v>34</v>
-      </c>
-      <c r="S143" t="s">
-        <v>39</v>
-      </c>
-      <c r="U143" t="s">
-        <v>30</v>
-      </c>
-      <c r="V143" t="s">
-        <v>34</v>
-      </c>
-      <c r="X143">
+      <c r="P143" t="s">
+        <v>38</v>
+      </c>
+      <c r="W143" t="s">
+        <v>39</v>
+      </c>
+      <c r="X143" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z143" t="s">
+        <v>34</v>
+      </c>
+      <c r="AA143" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB143">
         <v>13</v>
       </c>
     </row>
@@ -7495,7 +8116,7 @@
         <v>4</v>
       </c>
       <c r="C144" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D144">
         <v>3</v>
@@ -7507,33 +8128,36 @@
         <v>21</v>
       </c>
       <c r="G144" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H144" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I144" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J144">
         <v>4</v>
       </c>
       <c r="K144" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L144">
         <v>7</v>
       </c>
-      <c r="R144" t="s">
-        <v>30</v>
-      </c>
-      <c r="S144" t="s">
-        <v>74</v>
-      </c>
-      <c r="U144" t="s">
-        <v>30</v>
-      </c>
-      <c r="X144">
+      <c r="P144" t="s">
+        <v>70</v>
+      </c>
+      <c r="W144" t="s">
+        <v>34</v>
+      </c>
+      <c r="X144" t="s">
+        <v>87</v>
+      </c>
+      <c r="Z144" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB144">
         <v>13</v>
       </c>
     </row>
@@ -7545,7 +8169,7 @@
         <v>4</v>
       </c>
       <c r="C145" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D145">
         <v>4</v>
@@ -7557,15 +8181,15 @@
         <v>17</v>
       </c>
       <c r="G145" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H145" t="s">
-        <v>99</v>
+        <v>119</v>
       </c>
       <c r="I145" t="s">
-        <v>78</v>
-      </c>
-      <c r="X145">
+        <v>92</v>
+      </c>
+      <c r="AB145">
         <v>13</v>
       </c>
     </row>
@@ -7577,7 +8201,7 @@
         <v>4</v>
       </c>
       <c r="C146" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D146">
         <v>1</v>
@@ -7589,15 +8213,15 @@
         <v>-40</v>
       </c>
       <c r="G146" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H146" t="s">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="I146" t="s">
-        <v>28</v>
-      </c>
-      <c r="X146">
+        <v>32</v>
+      </c>
+      <c r="AB146">
         <v>13</v>
       </c>
     </row>
@@ -7609,7 +8233,7 @@
         <v>4</v>
       </c>
       <c r="C147" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D147">
         <v>1</v>
@@ -7621,19 +8245,19 @@
         <v>-20</v>
       </c>
       <c r="G147" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H147" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I147" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J147">
         <v>0</v>
       </c>
       <c r="K147" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L147">
         <v>5</v>
@@ -7644,19 +8268,25 @@
       <c r="O147">
         <v>4</v>
       </c>
-      <c r="R147" t="s">
-        <v>49</v>
-      </c>
-      <c r="S147" t="s">
-        <v>80</v>
-      </c>
-      <c r="U147" t="s">
-        <v>30</v>
-      </c>
-      <c r="W147">
-        <v>6</v>
-      </c>
-      <c r="X147">
+      <c r="P147" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q147" t="s">
+        <v>88</v>
+      </c>
+      <c r="S147">
+        <v>6</v>
+      </c>
+      <c r="W147" t="s">
+        <v>39</v>
+      </c>
+      <c r="X147" t="s">
+        <v>96</v>
+      </c>
+      <c r="Z147" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB147">
         <v>12</v>
       </c>
     </row>
@@ -7668,7 +8298,7 @@
         <v>4</v>
       </c>
       <c r="C148" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D148">
         <v>2</v>
@@ -7680,19 +8310,19 @@
         <v>-20</v>
       </c>
       <c r="G148" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H148" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I148" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="J148">
         <v>20</v>
       </c>
       <c r="K148" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L148">
         <v>6</v>
@@ -7703,19 +8333,25 @@
       <c r="O148">
         <v>4</v>
       </c>
-      <c r="R148" t="s">
-        <v>34</v>
-      </c>
-      <c r="S148" t="s">
-        <v>54</v>
-      </c>
-      <c r="U148" t="s">
-        <v>30</v>
-      </c>
-      <c r="W148">
-        <v>6</v>
-      </c>
-      <c r="X148">
+      <c r="P148" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q148" t="s">
+        <v>88</v>
+      </c>
+      <c r="S148">
+        <v>6</v>
+      </c>
+      <c r="W148" t="s">
+        <v>39</v>
+      </c>
+      <c r="X148" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z148" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB148">
         <v>12</v>
       </c>
     </row>
@@ -7727,7 +8363,7 @@
         <v>4</v>
       </c>
       <c r="C149" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D149">
         <v>1</v>
@@ -7739,36 +8375,42 @@
         <v>-40</v>
       </c>
       <c r="G149" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H149" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I149" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J149">
         <v>3</v>
       </c>
       <c r="K149" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L149">
         <v>6</v>
       </c>
-      <c r="R149" t="s">
-        <v>34</v>
-      </c>
-      <c r="S149" t="s">
-        <v>54</v>
-      </c>
-      <c r="U149" t="s">
-        <v>34</v>
-      </c>
-      <c r="W149">
-        <v>6</v>
-      </c>
-      <c r="X149">
+      <c r="P149" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q149" t="s">
+        <v>88</v>
+      </c>
+      <c r="S149">
+        <v>6</v>
+      </c>
+      <c r="W149" t="s">
+        <v>39</v>
+      </c>
+      <c r="X149" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z149" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB149">
         <v>12</v>
       </c>
     </row>
@@ -7780,7 +8422,7 @@
         <v>4</v>
       </c>
       <c r="C150" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D150">
         <v>2</v>
@@ -7792,19 +8434,19 @@
         <v>-43</v>
       </c>
       <c r="G150" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H150" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I150" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J150">
         <v>0</v>
       </c>
       <c r="K150" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L150">
         <v>5</v>
@@ -7815,19 +8457,25 @@
       <c r="O150">
         <v>9</v>
       </c>
-      <c r="R150" t="s">
-        <v>30</v>
-      </c>
-      <c r="S150" t="s">
-        <v>35</v>
-      </c>
-      <c r="U150" t="s">
-        <v>30</v>
-      </c>
-      <c r="W150">
-        <v>6</v>
-      </c>
-      <c r="X150">
+      <c r="P150" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q150" t="s">
+        <v>88</v>
+      </c>
+      <c r="S150">
+        <v>6</v>
+      </c>
+      <c r="W150" t="s">
+        <v>34</v>
+      </c>
+      <c r="X150" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z150" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB150">
         <v>12</v>
       </c>
     </row>
@@ -7839,7 +8487,7 @@
         <v>4</v>
       </c>
       <c r="C151" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D151">
         <v>3</v>
@@ -7851,19 +8499,19 @@
         <v>-43</v>
       </c>
       <c r="G151" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H151" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I151" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J151">
         <v>0</v>
       </c>
       <c r="K151" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L151">
         <v>7</v>
@@ -7874,19 +8522,25 @@
       <c r="O151">
         <v>4</v>
       </c>
-      <c r="R151" t="s">
-        <v>30</v>
-      </c>
-      <c r="S151" t="s">
-        <v>54</v>
-      </c>
-      <c r="U151" t="s">
-        <v>30</v>
-      </c>
-      <c r="W151">
-        <v>6</v>
-      </c>
-      <c r="X151">
+      <c r="P151" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q151" t="s">
+        <v>88</v>
+      </c>
+      <c r="S151">
+        <v>6</v>
+      </c>
+      <c r="W151" t="s">
+        <v>34</v>
+      </c>
+      <c r="X151" t="s">
+        <v>61</v>
+      </c>
+      <c r="Z151" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB151">
         <v>12</v>
       </c>
     </row>
@@ -7898,7 +8552,7 @@
         <v>4</v>
       </c>
       <c r="C152" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D152">
         <v>4</v>
@@ -7910,19 +8564,19 @@
         <v>-43</v>
       </c>
       <c r="G152" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H152" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="I152" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="J152">
         <v>0</v>
       </c>
       <c r="K152" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L152">
         <v>5</v>
@@ -7933,16 +8587,22 @@
       <c r="O152">
         <v>4</v>
       </c>
-      <c r="R152" t="s">
-        <v>30</v>
-      </c>
-      <c r="U152" t="s">
-        <v>30</v>
-      </c>
-      <c r="W152">
-        <v>6</v>
-      </c>
-      <c r="X152">
+      <c r="P152" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q152" t="s">
+        <v>88</v>
+      </c>
+      <c r="S152">
+        <v>6</v>
+      </c>
+      <c r="W152" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z152" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB152">
         <v>12</v>
       </c>
     </row>
@@ -7954,7 +8614,7 @@
         <v>4</v>
       </c>
       <c r="C153" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D153">
         <v>1</v>
@@ -7966,30 +8626,33 @@
         <v>43</v>
       </c>
       <c r="G153" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H153" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I153" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J153">
         <v>-6</v>
       </c>
       <c r="K153" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="L153">
         <v>8</v>
       </c>
-      <c r="R153" t="s">
-        <v>49</v>
-      </c>
-      <c r="S153" t="s">
-        <v>109</v>
-      </c>
-      <c r="X153">
+      <c r="P153" t="s">
+        <v>138</v>
+      </c>
+      <c r="W153" t="s">
+        <v>56</v>
+      </c>
+      <c r="X153" t="s">
+        <v>139</v>
+      </c>
+      <c r="AB153">
         <v>14</v>
       </c>
     </row>
